--- a/graficos_tabelas/preliminares/Tabela_resumo_thetas.xlsx
+++ b/graficos_tabelas/preliminares/Tabela_resumo_thetas.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6e8fc6e241c731ae/UFABC/Dissertação/volatilidade-IBOV-GPR/Impacto-geopolitico-ibovespa/graficos_tabelas/preliminares/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="174" documentId="11_F25DC773A252ABDACC1048C0F11B46C65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45B660C3-970E-44D8-826F-0144C5BDEDA2}"/>
+  <xr:revisionPtr revIDLastSave="424" documentId="11_F25DC773A252ABDACC1048C0F11B46C65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{597A7F39-3ED2-4E78-A415-D4C7156EE660}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IBOV" sheetId="1" r:id="rId1"/>
     <sheet name="SETORES" sheetId="2" r:id="rId2"/>
+    <sheet name="CONSUMO" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="148">
   <si>
     <t>Garch-Midas nos retornos do Ibovespa</t>
   </si>
@@ -179,6 +180,297 @@
   </si>
   <si>
     <t>-0.6884</t>
+  </si>
+  <si>
+    <t>SETOR DE ENERGIA  X GPR GLOBAL</t>
+  </si>
+  <si>
+    <t>-0.5515</t>
+  </si>
+  <si>
+    <t>0.0698</t>
+  </si>
+  <si>
+    <t>-0.2388</t>
+  </si>
+  <si>
+    <t>-0.1090</t>
+  </si>
+  <si>
+    <t>interpretação:</t>
+  </si>
+  <si>
+    <t>níveis mais altos de risco geopolítico global estão associados à volatilidade de longo prazo do setor/índice.</t>
+  </si>
+  <si>
+    <t>aumentos recentes no risco geopolítico global estão associados à volatilidade de longo prazo do setor/índice.</t>
+  </si>
+  <si>
+    <t>log(GPR)      → nível/patamar de tensão geopolítica</t>
+  </si>
+  <si>
+    <t>Δlog(GPR)     → variação recente/intensificação ou alívio da tensão</t>
+  </si>
+  <si>
+    <t>LOG-DIFF (GLOBAL)</t>
+  </si>
+  <si>
+    <t>0.0705</t>
+  </si>
+  <si>
+    <t>0.1859</t>
+  </si>
+  <si>
+    <t>0.1599</t>
+  </si>
+  <si>
+    <t>-0.2355</t>
+  </si>
+  <si>
+    <t>-0.3185</t>
+  </si>
+  <si>
+    <t>-0.0751</t>
+  </si>
+  <si>
+    <t>-0.5381</t>
+  </si>
+  <si>
+    <t>-0.0829</t>
+  </si>
+  <si>
+    <t>-0.0488</t>
+  </si>
+  <si>
+    <t>-0.0122</t>
+  </si>
+  <si>
+    <t>-0.0954</t>
+  </si>
+  <si>
+    <t>TRANSFORMAÇÃO</t>
+  </si>
+  <si>
+    <t>VARIAVEL (1)</t>
+  </si>
+  <si>
+    <t>K (1)</t>
+  </si>
+  <si>
+    <t>THETA 1</t>
+  </si>
+  <si>
+    <t>VARIAVEL (2)</t>
+  </si>
+  <si>
+    <t>K (2)</t>
+  </si>
+  <si>
+    <t>THETA 2</t>
+  </si>
+  <si>
+    <t>P-VALUE (1)</t>
+  </si>
+  <si>
+    <t>P-VALUE (2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GPR </t>
+  </si>
+  <si>
+    <t>CAMBIO</t>
+  </si>
+  <si>
+    <t>INTERPRETAÇÃO</t>
+  </si>
+  <si>
+    <t>-0.0614</t>
+  </si>
+  <si>
+    <t>-0.3352</t>
+  </si>
+  <si>
+    <t>0.909</t>
+  </si>
+  <si>
+    <t>0.027</t>
+  </si>
+  <si>
+    <t>-0.3522</t>
+  </si>
+  <si>
+    <t>0.035</t>
+  </si>
+  <si>
+    <t>-0.3765</t>
+  </si>
+  <si>
+    <t>0.000</t>
+  </si>
+  <si>
+    <t>-0.0883</t>
+  </si>
+  <si>
+    <t>0.510</t>
+  </si>
+  <si>
+    <t>-0.2664</t>
+  </si>
+  <si>
+    <t>0.006</t>
+  </si>
+  <si>
+    <t>MODELO 2 - GPR GLOBAL E VAR CAMBIO ASSIMÉTRICO</t>
+  </si>
+  <si>
+    <t>-0.1258</t>
+  </si>
+  <si>
+    <t>0.314</t>
+  </si>
+  <si>
+    <t>-0.1387</t>
+  </si>
+  <si>
+    <t>0.002</t>
+  </si>
+  <si>
+    <t>-0.1611</t>
+  </si>
+  <si>
+    <t>0.469</t>
+  </si>
+  <si>
+    <t>-0.7407</t>
+  </si>
+  <si>
+    <t>-0.3292</t>
+  </si>
+  <si>
+    <t>0.191</t>
+  </si>
+  <si>
+    <t>-0.3669</t>
+  </si>
+  <si>
+    <t>0.010</t>
+  </si>
+  <si>
+    <t>-0.0682</t>
+  </si>
+  <si>
+    <t>-0.1748</t>
+  </si>
+  <si>
+    <t>0.597</t>
+  </si>
+  <si>
+    <t>0.051</t>
+  </si>
+  <si>
+    <t>-0.0934</t>
+  </si>
+  <si>
+    <t>-0.0396</t>
+  </si>
+  <si>
+    <t>0.457</t>
+  </si>
+  <si>
+    <t>0.218</t>
+  </si>
+  <si>
+    <t>-0.7305</t>
+  </si>
+  <si>
+    <t>-0.3105</t>
+  </si>
+  <si>
+    <t>0.603</t>
+  </si>
+  <si>
+    <t>0.020</t>
+  </si>
+  <si>
+    <t>0.0791</t>
+  </si>
+  <si>
+    <t>-0.3640</t>
+  </si>
+  <si>
+    <t>0.599</t>
+  </si>
+  <si>
+    <t>0.017</t>
+  </si>
+  <si>
+    <t>0.3654</t>
+  </si>
+  <si>
+    <t>-0.2685</t>
+  </si>
+  <si>
+    <t>0.185</t>
+  </si>
+  <si>
+    <t>0.4287</t>
+  </si>
+  <si>
+    <t>-0.1361</t>
+  </si>
+  <si>
+    <t>0.135</t>
+  </si>
+  <si>
+    <t>0.004</t>
+  </si>
+  <si>
+    <t>-0.1714</t>
+  </si>
+  <si>
+    <t>-0.7519</t>
+  </si>
+  <si>
+    <t>0.419</t>
+  </si>
+  <si>
+    <t>0.2094</t>
+  </si>
+  <si>
+    <t>-0.3697</t>
+  </si>
+  <si>
+    <t>0.513</t>
+  </si>
+  <si>
+    <t>0.011</t>
+  </si>
+  <si>
+    <t>0.4160</t>
+  </si>
+  <si>
+    <t>-0.1530</t>
+  </si>
+  <si>
+    <t>0.163</t>
+  </si>
+  <si>
+    <t>0.105</t>
+  </si>
+  <si>
+    <t>0.4697</t>
+  </si>
+  <si>
+    <t>-0.0425</t>
+  </si>
+  <si>
+    <t>0.103</t>
+  </si>
+  <si>
+    <t>0.178</t>
+  </si>
+  <si>
+    <t>MODELO 2 - GPR GLOBAL E VAR CAMBIO ASSIMÉTRICO - SETOR: CONSUMO</t>
   </si>
 </sst>
 </file>
@@ -194,7 +486,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -204,6 +496,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -246,17 +544,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -272,6 +572,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -537,32 +841,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="99.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>1</v>
       </c>
@@ -573,7 +882,7 @@
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -596,37 +905,37 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D8" s="1"/>
@@ -634,7 +943,7 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -657,8 +966,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -680,7 +989,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>25</v>
       </c>
@@ -691,7 +1000,7 @@
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>24</v>
       </c>
@@ -714,14 +1023,14 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B15" s="1">
         <v>0</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D15" s="1" t="s">
@@ -736,11 +1045,17 @@
       <c r="G15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="2" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J15" t="s">
+        <v>56</v>
+      </c>
+      <c r="K15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>6</v>
       </c>
@@ -765,8 +1080,14 @@
       <c r="H16" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="J16" t="s">
+        <v>56</v>
+      </c>
+      <c r="K16" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>7</v>
       </c>
@@ -792,8 +1113,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -811,14 +1132,576 @@
       <c r="F18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="3" t="s">
         <v>10</v>
       </c>
     </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="K21" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="1">
+        <v>12</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="1">
+        <v>12</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="1">
+        <v>6</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" s="1">
+        <v>6</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="1">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" s="1">
+        <v>3</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="1">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="5">
+        <v>12</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" s="5">
+        <v>12</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H26" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>6</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" s="5">
+        <v>6</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" s="5">
+        <v>3</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" s="5">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="5">
+        <v>12</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F30" s="5">
+        <v>12</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="5">
+        <v>6</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F31" s="5">
+        <v>6</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="5">
+        <v>3</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F32" s="5">
+        <v>3</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="H32" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="5">
+        <v>3</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F33" s="5">
+        <v>1</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H33" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="5">
+        <v>12</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F34" s="5">
+        <v>12</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H34" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="5">
+        <v>6</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" s="5">
+        <v>6</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="5">
+        <v>3</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F36" s="5">
+        <v>3</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="H36" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="5">
+        <v>3</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F37" s="5">
+        <v>1</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A20:J20"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -826,7 +1709,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D2415F-2C74-4FBC-80F5-D0FED7D6FFCB}">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
@@ -840,182 +1723,896 @@
         <v>38</v>
       </c>
     </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>59</v>
+      </c>
+    </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="B6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="6"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="6"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="8">
+        <v>-1190</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A21:G21"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEBFC21E-638D-46A4-9310-2596796FD0AF}">
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>61</v>
+      </c>
       <c r="B4" s="1" t="s">
-        <v>2</v>
+        <v>65</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>3</v>
+        <v>66</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="1">
         <v>12</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D8" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="1">
+        <v>12</v>
+      </c>
+      <c r="G8" s="5"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="C9" s="1">
+        <v>6</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>3</v>
+        <v>83</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="1">
+        <v>6</v>
+      </c>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="1">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" s="1">
+        <v>3</v>
+      </c>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="1">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1</v>
+      </c>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="5">
         <v>12</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D12" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="5">
+        <v>12</v>
+      </c>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="C13" s="5">
+        <v>6</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F13" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" s="5">
+        <v>6</v>
+      </c>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="5">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" s="5">
+        <v>3</v>
+      </c>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="5">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" s="5">
+        <v>1</v>
+      </c>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="5">
         <v>12</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="D16" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" s="5">
+        <v>12</v>
+      </c>
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="5">
+        <v>6</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" s="5">
+        <v>6</v>
+      </c>
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="5">
+        <v>3</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" s="5">
+        <v>3</v>
+      </c>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="5">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" s="5">
+        <v>1</v>
+      </c>
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="5">
+        <v>12</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" s="5">
+        <v>12</v>
+      </c>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="5">
+        <v>6</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" s="5">
+        <v>6</v>
+      </c>
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="5">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" s="5">
+        <v>3</v>
+      </c>
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="5">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23" s="5">
+        <v>1</v>
+      </c>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A12:G12"/>
+  <mergeCells count="2">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A6:J6"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/graficos_tabelas/preliminares/Tabela_resumo_thetas.xlsx
+++ b/graficos_tabelas/preliminares/Tabela_resumo_thetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6e8fc6e241c731ae/UFABC/Dissertação/volatilidade-IBOV-GPR/Impacto-geopolitico-ibovespa/graficos_tabelas/preliminares/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="424" documentId="11_F25DC773A252ABDACC1048C0F11B46C65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{597A7F39-3ED2-4E78-A415-D4C7156EE660}"/>
+  <xr:revisionPtr revIDLastSave="489" documentId="11_F25DC773A252ABDACC1048C0F11B46C65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B564CA41-16C4-4F40-818E-75134AF8700E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="182">
   <si>
     <t>Garch-Midas nos retornos do Ibovespa</t>
   </si>
@@ -471,6 +471,108 @@
   </si>
   <si>
     <t>MODELO 2 - GPR GLOBAL E VAR CAMBIO ASSIMÉTRICO - SETOR: CONSUMO</t>
+  </si>
+  <si>
+    <t>SETOR CONSUMO X CAMBIO</t>
+  </si>
+  <si>
+    <t>LOG (CAMBIO)</t>
+  </si>
+  <si>
+    <t>LOG-DIFF (CAMBIO</t>
+  </si>
+  <si>
+    <t>-0.1231</t>
+  </si>
+  <si>
+    <t>0.285</t>
+  </si>
+  <si>
+    <t>-0.1541</t>
+  </si>
+  <si>
+    <t>0.254</t>
+  </si>
+  <si>
+    <t>-0.1905</t>
+  </si>
+  <si>
+    <t>0.123</t>
+  </si>
+  <si>
+    <t>K = 1</t>
+  </si>
+  <si>
+    <t>-0.1055</t>
+  </si>
+  <si>
+    <t>0.791</t>
+  </si>
+  <si>
+    <t>0.2436</t>
+  </si>
+  <si>
+    <t>0.748</t>
+  </si>
+  <si>
+    <t>0.1627</t>
+  </si>
+  <si>
+    <t>0.900</t>
+  </si>
+  <si>
+    <t>GPR GLOBAL - Simétrico</t>
+  </si>
+  <si>
+    <t>-0.5958</t>
+  </si>
+  <si>
+    <t>0.056</t>
+  </si>
+  <si>
+    <t>-0.6991</t>
+  </si>
+  <si>
+    <t>0.014</t>
+  </si>
+  <si>
+    <t>-0.3520</t>
+  </si>
+  <si>
+    <t>0.864</t>
+  </si>
+  <si>
+    <t>0.770</t>
+  </si>
+  <si>
+    <t>0.422</t>
+  </si>
+  <si>
+    <t>-0.005</t>
+  </si>
+  <si>
+    <t>0.333</t>
+  </si>
+  <si>
+    <t>0.2663</t>
+  </si>
+  <si>
+    <t>0.128</t>
+  </si>
+  <si>
+    <t>0.4960</t>
+  </si>
+  <si>
+    <t>0.089</t>
+  </si>
+  <si>
+    <t>0.344</t>
+  </si>
+  <si>
+    <t>0.100</t>
+  </si>
+  <si>
+    <t>0.154</t>
   </si>
 </sst>
 </file>
@@ -506,7 +608,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -540,6 +642,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -549,14 +671,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -841,7 +967,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -856,33 +982,33 @@
     <col min="11" max="11" width="99.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -905,7 +1031,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -928,7 +1054,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -943,7 +1069,7 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -966,7 +1092,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -989,328 +1115,280 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="1">
-        <v>0</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="1">
-        <v>0</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J15" t="s">
-        <v>56</v>
-      </c>
-      <c r="K15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H16" t="s">
-        <v>28</v>
-      </c>
-      <c r="J16" t="s">
-        <v>56</v>
-      </c>
-      <c r="K16" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H17" t="s">
-        <v>28</v>
-      </c>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="1">
+        <v>0</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J19" t="s">
+        <v>56</v>
+      </c>
+      <c r="K19" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
+      <c r="A20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="H20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J20" t="s">
+        <v>56</v>
+      </c>
+      <c r="K20" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>74</v>
+        <v>7</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>75</v>
+        <v>171</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>73</v>
+        <v>172</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="K21" t="s">
-        <v>84</v>
+        <v>176</v>
+      </c>
+      <c r="H21" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>82</v>
+        <v>8</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="1">
-        <v>12</v>
+        <v>33</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" s="1">
-        <v>12</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="1">
-        <v>6</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" s="1">
-        <v>6</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>92</v>
+        <v>16</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="1">
-        <v>3</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" s="1">
-        <v>3</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>96</v>
-      </c>
+      <c r="A24" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="1">
-        <v>3</v>
+        <v>73</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" s="1">
-        <v>1</v>
+        <v>73</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>101</v>
+        <v>79</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="K25" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1320,29 +1398,29 @@
       <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="1">
         <v>12</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" s="5">
+      <c r="E26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26" s="1">
         <v>12</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="H26" s="5" t="s">
-        <v>103</v>
+        <v>85</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>87</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>104</v>
+        <v>86</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -1352,29 +1430,29 @@
       <c r="B27" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C27" s="1">
         <v>6</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" s="5">
+      <c r="E27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F27" s="1">
         <v>6</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>106</v>
+        <v>89</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>90</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1384,29 +1462,29 @@
       <c r="B28" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="1">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" s="5">
+      <c r="E28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F28" s="1">
         <v>3</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>111</v>
+        <v>93</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="J28" s="9" t="s">
-        <v>112</v>
+        <v>95</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1416,29 +1494,29 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="5">
+      <c r="C29" s="1">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E29" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" s="5">
+      <c r="E29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F29" s="1">
         <v>1</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>115</v>
+        <v>98</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>116</v>
+        <v>100</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1446,31 +1524,31 @@
         <v>82</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="5">
+        <v>6</v>
+      </c>
+      <c r="C30" s="1">
         <v>12</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" s="5">
+      <c r="E30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" s="1">
         <v>12</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>119</v>
+        <v>102</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1478,31 +1556,31 @@
         <v>82</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="5">
+        <v>6</v>
+      </c>
+      <c r="C31" s="1">
         <v>6</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" s="5">
+      <c r="E31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F31" s="1">
         <v>6</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>123</v>
+        <v>105</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>106</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -1510,31 +1588,31 @@
         <v>82</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="5">
+        <v>6</v>
+      </c>
+      <c r="C32" s="1">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E32" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" s="5">
+      <c r="E32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F32" s="1">
         <v>3</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>127</v>
+        <v>109</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>111</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>96</v>
+        <v>110</v>
+      </c>
+      <c r="J32" s="5" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -1542,31 +1620,31 @@
         <v>82</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="5">
+        <v>6</v>
+      </c>
+      <c r="C33" s="1">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E33" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" s="5">
+      <c r="E33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F33" s="1">
         <v>1</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>130</v>
+        <v>113</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>131</v>
+        <v>114</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -1576,29 +1654,29 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="5">
+      <c r="C34" s="1">
         <v>12</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E34" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" s="5">
+      <c r="E34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F34" s="1">
         <v>12</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>134</v>
+        <v>117</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -1608,29 +1686,29 @@
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="5">
+      <c r="C35" s="1">
         <v>6</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E35" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" s="5">
+      <c r="E35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F35" s="1">
         <v>6</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>137</v>
+        <v>121</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -1640,29 +1718,29 @@
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="5">
+      <c r="C36" s="1">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E36" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" s="5">
+      <c r="E36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F36" s="1">
         <v>3</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>141</v>
+        <v>125</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J36" s="5" t="s">
-        <v>142</v>
+        <v>126</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -1672,36 +1750,165 @@
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C37" s="5">
+      <c r="C37" s="1">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E37" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" s="5">
+      <c r="E37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F37" s="1">
         <v>1</v>
       </c>
       <c r="G37" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="1">
+        <v>12</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F38" s="1">
+        <v>12</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="1">
+        <v>6</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F39" s="1">
+        <v>6</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="1">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F40" s="1">
+        <v>3</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="1">
+        <v>3</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F41" s="1">
+        <v>1</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="H37" s="5" t="s">
+      <c r="H41" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="I37" s="1" t="s">
+      <c r="I41" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="J37" s="5" t="s">
+      <c r="J41" s="1" t="s">
         <v>146</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A12:G12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1734,15 +1941,15 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -1791,7 +1998,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -1814,15 +2021,15 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -1871,7 +2078,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -1893,34 +2100,16 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="6"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="6"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-    </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -1969,10 +2158,10 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="4">
         <v>-1190</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -1992,15 +2181,15 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -2032,13 +2221,13 @@
       <c r="B23" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="1" t="s">
@@ -2049,7 +2238,7 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -2084,7 +2273,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEBFC21E-638D-46A4-9310-2596796FD0AF}">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.140625" bestFit="1" customWidth="1"/>
@@ -2095,20 +2284,20 @@
     <col min="6" max="6" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2157,7 +2346,7 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -2180,194 +2369,134 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
+      <c r="A6" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>73</v>
+        <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>77</v>
+        <v>3</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>80</v>
+        <v>157</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>81</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="1">
-        <v>12</v>
+        <v>151</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>152</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" s="1">
-        <v>12</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
+        <v>153</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="1">
-        <v>6</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="1">
-        <v>6</v>
-      </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="1">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="1">
-        <v>3</v>
-      </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="1">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" s="1">
-        <v>1</v>
-      </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5"/>
+        <v>150</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="5">
-        <v>12</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="5">
-        <v>12</v>
-      </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-      <c r="J12" s="5"/>
+      <c r="A12" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="5">
-        <v>6</v>
+        <v>73</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" s="5">
-        <v>6</v>
-      </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
+        <v>77</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
@@ -2376,22 +2505,30 @@
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="5">
-        <v>3</v>
+      <c r="C14" s="1">
+        <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" s="5">
-        <v>3</v>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
+      <c r="E14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="1">
+        <v>12</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
@@ -2400,166 +2537,166 @@
       <c r="B15" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="5">
-        <v>3</v>
+      <c r="C15" s="1">
+        <v>6</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" s="5">
-        <v>1</v>
-      </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
-      <c r="I15" s="5"/>
-      <c r="J15" s="5"/>
+      <c r="E15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" s="1">
+        <v>6</v>
+      </c>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="5">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="C16" s="1">
+        <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" s="5">
-        <v>12</v>
-      </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5"/>
-      <c r="J16" s="5"/>
+      <c r="E16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" s="1">
+        <v>3</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="5">
-        <v>6</v>
+        <v>6</v>
+      </c>
+      <c r="C17" s="1">
+        <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E17" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" s="5">
-        <v>6</v>
-      </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5"/>
-      <c r="J17" s="5"/>
+      <c r="E17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="5">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="C18" s="1">
+        <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" s="5">
-        <v>3</v>
-      </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
+      <c r="E18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" s="1">
+        <v>12</v>
+      </c>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="5">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="C19" s="1">
+        <v>6</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E19" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" s="5">
-        <v>1</v>
-      </c>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
+      <c r="E19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" s="1">
+        <v>6</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="5">
-        <v>12</v>
+        <v>6</v>
+      </c>
+      <c r="C20" s="1">
+        <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" s="5">
-        <v>12</v>
-      </c>
-      <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
+      <c r="E20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" s="1">
+        <v>3</v>
+      </c>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>82</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="5">
-        <v>6</v>
+        <v>6</v>
+      </c>
+      <c r="C21" s="1">
+        <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" s="5">
-        <v>6</v>
-      </c>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
+      <c r="E21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -2568,22 +2705,22 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="5">
-        <v>3</v>
+      <c r="C22" s="1">
+        <v>12</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" s="5">
-        <v>3</v>
-      </c>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5"/>
-      <c r="J22" s="5"/>
+      <c r="E22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="1">
+        <v>12</v>
+      </c>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
@@ -2592,27 +2729,172 @@
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="5">
-        <v>3</v>
+      <c r="C23" s="1">
+        <v>6</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" s="5">
+      <c r="E23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" s="1">
+        <v>6</v>
+      </c>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="1">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" s="1">
+        <v>3</v>
+      </c>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="1">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" s="1">
         <v>1</v>
       </c>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="1">
+        <v>12</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" s="1">
+        <v>12</v>
+      </c>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="1">
+        <v>6</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" s="1">
+        <v>6</v>
+      </c>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="1">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" s="1">
+        <v>3</v>
+      </c>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="1">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1</v>
+      </c>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A6:I6"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/graficos_tabelas/preliminares/Tabela_resumo_thetas.xlsx
+++ b/graficos_tabelas/preliminares/Tabela_resumo_thetas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6e8fc6e241c731ae/UFABC/Dissertação/volatilidade-IBOV-GPR/Impacto-geopolitico-ibovespa/graficos_tabelas/preliminares/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="489" documentId="11_F25DC773A252ABDACC1048C0F11B46C65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B564CA41-16C4-4F40-818E-75134AF8700E}"/>
+  <xr:revisionPtr revIDLastSave="575" documentId="11_F25DC773A252ABDACC1048C0F11B46C65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0412E99C-3BB9-4011-8056-68D0DCB2BDC1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IBOV" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="243">
   <si>
     <t>Garch-Midas nos retornos do Ibovespa</t>
   </si>
@@ -573,6 +573,189 @@
   </si>
   <si>
     <t>0.154</t>
+  </si>
+  <si>
+    <t>0.2134</t>
+  </si>
+  <si>
+    <t>-0.1030</t>
+  </si>
+  <si>
+    <t>0.0733</t>
+  </si>
+  <si>
+    <t>0.962</t>
+  </si>
+  <si>
+    <t>-0.1241</t>
+  </si>
+  <si>
+    <t>0.308</t>
+  </si>
+  <si>
+    <t>0.0769</t>
+  </si>
+  <si>
+    <t>0.475</t>
+  </si>
+  <si>
+    <t>-0.1047</t>
+  </si>
+  <si>
+    <t>0.025</t>
+  </si>
+  <si>
+    <t>0.3810</t>
+  </si>
+  <si>
+    <t>0.195</t>
+  </si>
+  <si>
+    <t>-0.6530</t>
+  </si>
+  <si>
+    <t>0.065</t>
+  </si>
+  <si>
+    <t>0.2756</t>
+  </si>
+  <si>
+    <t>0.055</t>
+  </si>
+  <si>
+    <t>-0.3418</t>
+  </si>
+  <si>
+    <t>0.030</t>
+  </si>
+  <si>
+    <t>0.0924</t>
+  </si>
+  <si>
+    <t>0.664</t>
+  </si>
+  <si>
+    <t>-0.1545</t>
+  </si>
+  <si>
+    <t>0.951</t>
+  </si>
+  <si>
+    <t>0.1332</t>
+  </si>
+  <si>
+    <t>-0.0560</t>
+  </si>
+  <si>
+    <t>0.048</t>
+  </si>
+  <si>
+    <t>0.039</t>
+  </si>
+  <si>
+    <t>0.569</t>
+  </si>
+  <si>
+    <t>0.813</t>
+  </si>
+  <si>
+    <t>0.583</t>
+  </si>
+  <si>
+    <t>0.704</t>
+  </si>
+  <si>
+    <t>-0.6707</t>
+  </si>
+  <si>
+    <t>0.517</t>
+  </si>
+  <si>
+    <t>-0.1619</t>
+  </si>
+  <si>
+    <t>0.117</t>
+  </si>
+  <si>
+    <t>-0.3896</t>
+  </si>
+  <si>
+    <t>0.478</t>
+  </si>
+  <si>
+    <t>-0.1556</t>
+  </si>
+  <si>
+    <t>0.282</t>
+  </si>
+  <si>
+    <t>-0.0960</t>
+  </si>
+  <si>
+    <t>0.464</t>
+  </si>
+  <si>
+    <t>-0.1200</t>
+  </si>
+  <si>
+    <t>0.141</t>
+  </si>
+  <si>
+    <t>-0.0876</t>
+  </si>
+  <si>
+    <t>0.501</t>
+  </si>
+  <si>
+    <t>-0.1084</t>
+  </si>
+  <si>
+    <t>-0.1867</t>
+  </si>
+  <si>
+    <t>0.502</t>
+  </si>
+  <si>
+    <t>-0.7154</t>
+  </si>
+  <si>
+    <t>0.068</t>
+  </si>
+  <si>
+    <t>-0.1456</t>
+  </si>
+  <si>
+    <t>0.607</t>
+  </si>
+  <si>
+    <t>-0.3505</t>
+  </si>
+  <si>
+    <t>0.024</t>
+  </si>
+  <si>
+    <t>-0.0763</t>
+  </si>
+  <si>
+    <t>0.740</t>
+  </si>
+  <si>
+    <t>-0.1568</t>
+  </si>
+  <si>
+    <t>0.074</t>
+  </si>
+  <si>
+    <t>-0.0380</t>
+  </si>
+  <si>
+    <t>0.708</t>
+  </si>
+  <si>
+    <t>-0.0521</t>
+  </si>
+  <si>
+    <t>0.066</t>
   </si>
 </sst>
 </file>
@@ -666,7 +849,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -676,7 +859,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1274,7 +1456,7 @@
       <c r="D20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="5" t="s">
         <v>180</v>
       </c>
       <c r="F20" s="1" t="s">
@@ -1893,7 +2075,7 @@
       <c r="G41" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H41" s="5" t="s">
         <v>145</v>
       </c>
       <c r="I41" s="1" t="s">
@@ -2062,19 +2244,19 @@
         <v>45</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>10</v>
+        <v>207</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>16</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -2085,19 +2267,19 @@
         <v>65</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>16</v>
+        <v>209</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>66</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>16</v>
+        <v>210</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>67</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>16</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -2330,19 +2512,19 @@
         <v>45</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>10</v>
+        <v>207</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>47</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>16</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -2353,33 +2535,33 @@
         <v>65</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>209</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>66</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
+        <v>210</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>67</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>16</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -2417,13 +2599,13 @@
       <c r="B8" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="1" t="s">
         <v>152</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="1" t="s">
         <v>154</v>
       </c>
       <c r="F8" s="1" t="s">
@@ -2549,10 +2731,18 @@
       <c r="F15" s="1">
         <v>6</v>
       </c>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -2573,10 +2763,18 @@
       <c r="F16" s="1">
         <v>3</v>
       </c>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
+      <c r="G16" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -2597,10 +2795,18 @@
       <c r="F17" s="1">
         <v>1</v>
       </c>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
+      <c r="G17" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -2621,10 +2827,18 @@
       <c r="F18" s="1">
         <v>12</v>
       </c>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
+      <c r="G18" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
@@ -2645,10 +2859,18 @@
       <c r="F19" s="1">
         <v>6</v>
       </c>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
+      <c r="G19" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -2669,10 +2891,18 @@
       <c r="F20" s="1">
         <v>3</v>
       </c>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
+      <c r="G20" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
@@ -2693,10 +2923,18 @@
       <c r="F21" s="1">
         <v>1</v>
       </c>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
+      <c r="G21" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -2717,10 +2955,18 @@
       <c r="F22" s="1">
         <v>12</v>
       </c>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
+      <c r="G22" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
@@ -2741,10 +2987,18 @@
       <c r="F23" s="1">
         <v>6</v>
       </c>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
+      <c r="G23" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>219</v>
+      </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
@@ -2765,10 +3019,18 @@
       <c r="F24" s="1">
         <v>3</v>
       </c>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
+      <c r="G24" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
@@ -2789,10 +3051,18 @@
       <c r="F25" s="1">
         <v>1</v>
       </c>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
+      <c r="G25" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
@@ -2813,10 +3083,18 @@
       <c r="F26" s="1">
         <v>12</v>
       </c>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
+      <c r="G26" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
@@ -2837,10 +3115,18 @@
       <c r="F27" s="1">
         <v>6</v>
       </c>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
+      <c r="G27" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
@@ -2861,10 +3147,18 @@
       <c r="F28" s="1">
         <v>3</v>
       </c>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
+      <c r="G28" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="J28" s="5" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
@@ -2885,10 +3179,18 @@
       <c r="F29" s="1">
         <v>1</v>
       </c>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
+      <c r="G29" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>242</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/graficos_tabelas/preliminares/Tabela_resumo_thetas.xlsx
+++ b/graficos_tabelas/preliminares/Tabela_resumo_thetas.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6e8fc6e241c731ae/UFABC/Dissertação/volatilidade-IBOV-GPR/Impacto-geopolitico-ibovespa/graficos_tabelas/preliminares/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="575" documentId="11_F25DC773A252ABDACC1048C0F11B46C65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0412E99C-3BB9-4011-8056-68D0DCB2BDC1}"/>
+  <xr:revisionPtr revIDLastSave="654" documentId="11_F25DC773A252ABDACC1048C0F11B46C65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30B98A5B-EB48-4703-957F-A9EA5F3A3E90}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IBOV" sheetId="1" r:id="rId1"/>
     <sheet name="SETORES" sheetId="2" r:id="rId2"/>
     <sheet name="CONSUMO" sheetId="3" r:id="rId3"/>
+    <sheet name="BENS BASICOS" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="277">
   <si>
     <t>Garch-Midas nos retornos do Ibovespa</t>
   </si>
@@ -756,6 +757,108 @@
   </si>
   <si>
     <t>0.066</t>
+  </si>
+  <si>
+    <t>SETOR BENS BASICOS X CAMBIO</t>
+  </si>
+  <si>
+    <t>MODELO 2 - GPR GLOBAL E VAR CAMBIO ASSIMÉTRICO - SETOR: BENS BASICOS</t>
+  </si>
+  <si>
+    <t>0.1558</t>
+  </si>
+  <si>
+    <t>0.186</t>
+  </si>
+  <si>
+    <t>-0.1153</t>
+  </si>
+  <si>
+    <t>0.019</t>
+  </si>
+  <si>
+    <t>-0.1218</t>
+  </si>
+  <si>
+    <t>0.009</t>
+  </si>
+  <si>
+    <t>-0.4601</t>
+  </si>
+  <si>
+    <t>-0.3733</t>
+  </si>
+  <si>
+    <t>0.243</t>
+  </si>
+  <si>
+    <t>-0.2644</t>
+  </si>
+  <si>
+    <t>-0.0636</t>
+  </si>
+  <si>
+    <t>0.069</t>
+  </si>
+  <si>
+    <t>-0.6628</t>
+  </si>
+  <si>
+    <t>0.001</t>
+  </si>
+  <si>
+    <t>0.2691</t>
+  </si>
+  <si>
+    <t>-0.6661</t>
+  </si>
+  <si>
+    <t>0.003</t>
+  </si>
+  <si>
+    <t>-0.0843</t>
+  </si>
+  <si>
+    <t>0.143</t>
+  </si>
+  <si>
+    <t>-0.4793</t>
+  </si>
+  <si>
+    <t>-0.0974</t>
+  </si>
+  <si>
+    <t>0.106</t>
+  </si>
+  <si>
+    <t>-0.4883</t>
+  </si>
+  <si>
+    <t>0.054</t>
+  </si>
+  <si>
+    <t>-0.0956</t>
+  </si>
+  <si>
+    <t>0.086</t>
+  </si>
+  <si>
+    <t>-0.5405</t>
+  </si>
+  <si>
+    <t>-0.3608</t>
+  </si>
+  <si>
+    <t>0.088</t>
+  </si>
+  <si>
+    <t>-0.6781</t>
+  </si>
+  <si>
+    <t>-0.3974</t>
+  </si>
+  <si>
+    <t>0.205</t>
   </si>
 </sst>
 </file>
@@ -849,7 +952,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -865,6 +968,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3200,4 +3304,689 @@
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF7E7DD8-1A46-4903-B932-981461A1B017}">
+  <dimension ref="A1:J29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B4" s="4">
+        <v>-1190</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="1">
+        <v>12</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="1">
+        <v>12</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="1">
+        <v>6</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" s="1">
+        <v>6</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="I15" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="1">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" s="1">
+        <v>3</v>
+      </c>
+      <c r="G16" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="1">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="1">
+        <v>12</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" s="1">
+        <v>12</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I18" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="1">
+        <v>6</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" s="1">
+        <v>6</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="1">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" s="1">
+        <v>3</v>
+      </c>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="1">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="1">
+        <v>12</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="1">
+        <v>12</v>
+      </c>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="1">
+        <v>6</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" s="1">
+        <v>6</v>
+      </c>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="1">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" s="1">
+        <v>3</v>
+      </c>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="1">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="1">
+        <v>12</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" s="1">
+        <v>12</v>
+      </c>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="1">
+        <v>6</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" s="1">
+        <v>6</v>
+      </c>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="1">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" s="1">
+        <v>3</v>
+      </c>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="1">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1</v>
+      </c>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A12:J12"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/graficos_tabelas/preliminares/Tabela_resumo_thetas.xlsx
+++ b/graficos_tabelas/preliminares/Tabela_resumo_thetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6e8fc6e241c731ae/UFABC/Dissertação/volatilidade-IBOV-GPR/Impacto-geopolitico-ibovespa/graficos_tabelas/preliminares/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="654" documentId="11_F25DC773A252ABDACC1048C0F11B46C65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30B98A5B-EB48-4703-957F-A9EA5F3A3E90}"/>
+  <xr:revisionPtr revIDLastSave="713" documentId="11_F25DC773A252ABDACC1048C0F11B46C65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D66360B2-ED2D-400F-8760-1D3321899FE1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="308">
   <si>
     <t>Garch-Midas nos retornos do Ibovespa</t>
   </si>
@@ -859,6 +859,99 @@
   </si>
   <si>
     <t>0.205</t>
+  </si>
+  <si>
+    <t>-0.4791</t>
+  </si>
+  <si>
+    <t>-0.2767</t>
+  </si>
+  <si>
+    <t>-0.5350</t>
+  </si>
+  <si>
+    <t>0.008</t>
+  </si>
+  <si>
+    <t>-0.0628</t>
+  </si>
+  <si>
+    <t>0.072</t>
+  </si>
+  <si>
+    <t>0.300</t>
+  </si>
+  <si>
+    <t>0.0083</t>
+  </si>
+  <si>
+    <t>0.087</t>
+  </si>
+  <si>
+    <t>-0.4346</t>
+  </si>
+  <si>
+    <t>0.482</t>
+  </si>
+  <si>
+    <t>-0.1174</t>
+  </si>
+  <si>
+    <t>0.029</t>
+  </si>
+  <si>
+    <t>-0.1203</t>
+  </si>
+  <si>
+    <t>0.387</t>
+  </si>
+  <si>
+    <t>-0.1288</t>
+  </si>
+  <si>
+    <t>-0.1205</t>
+  </si>
+  <si>
+    <t>0.365</t>
+  </si>
+  <si>
+    <t>0.007</t>
+  </si>
+  <si>
+    <t>0.244</t>
+  </si>
+  <si>
+    <t>-0.4669</t>
+  </si>
+  <si>
+    <t>-0.5964</t>
+  </si>
+  <si>
+    <t>-0.3770</t>
+  </si>
+  <si>
+    <t>0.245</t>
+  </si>
+  <si>
+    <t>-0.1554</t>
+  </si>
+  <si>
+    <t>0.343</t>
+  </si>
+  <si>
+    <t>-0.2732</t>
+  </si>
+  <si>
+    <t>0.4192</t>
+  </si>
+  <si>
+    <t>0.647</t>
+  </si>
+  <si>
+    <t>-0.0692</t>
+  </si>
+  <si>
+    <t>0.063</t>
   </si>
 </sst>
 </file>
@@ -968,7 +1061,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3568,13 +3663,13 @@
       <c r="F14" s="1">
         <v>12</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="1" t="s">
         <v>257</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="I14" s="1" t="s">
         <v>259</v>
       </c>
       <c r="J14" s="3" t="s">
@@ -3600,16 +3695,16 @@
       <c r="F15" s="1">
         <v>6</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="1" t="s">
         <v>260</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="I15" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="J15" s="9" t="s">
+      <c r="J15" s="1" t="s">
         <v>263</v>
       </c>
     </row>
@@ -3632,13 +3727,13 @@
       <c r="F16" s="1">
         <v>3</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="G16" s="1" t="s">
         <v>264</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="I16" s="9" t="s">
+      <c r="I16" s="1" t="s">
         <v>265</v>
       </c>
       <c r="J16" s="5" t="s">
@@ -3664,13 +3759,13 @@
       <c r="F17" s="1">
         <v>1</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="1" t="s">
         <v>267</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="I17" s="9" t="s">
+      <c r="I17" s="1" t="s">
         <v>269</v>
       </c>
       <c r="J17" s="5" t="s">
@@ -3696,13 +3791,13 @@
       <c r="F18" s="1">
         <v>12</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="1" t="s">
         <v>271</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="I18" s="1" t="s">
         <v>272</v>
       </c>
       <c r="J18" s="5" t="s">
@@ -3728,16 +3823,16 @@
       <c r="F19" s="1">
         <v>6</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="1" t="s">
         <v>274</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="I19" s="9" t="s">
+      <c r="I19" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="J19" s="9" t="s">
+      <c r="J19" s="1" t="s">
         <v>276</v>
       </c>
     </row>
@@ -3760,10 +3855,18 @@
       <c r="F20" s="1">
         <v>3</v>
       </c>
-      <c r="G20" s="9"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
+      <c r="G20" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
@@ -3784,10 +3887,18 @@
       <c r="F21" s="1">
         <v>1</v>
       </c>
-      <c r="G21" s="9"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
+      <c r="G21" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -3808,10 +3919,18 @@
       <c r="F22" s="1">
         <v>12</v>
       </c>
-      <c r="G22" s="9"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
+      <c r="G22" s="9">
+        <v>-1339</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>285</v>
+      </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
@@ -3832,10 +3951,18 @@
       <c r="F23" s="1">
         <v>6</v>
       </c>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
+      <c r="G23" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>289</v>
+      </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
@@ -3856,10 +3983,18 @@
       <c r="F24" s="1">
         <v>3</v>
       </c>
-      <c r="G24" s="9"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
+      <c r="G24" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
@@ -3880,10 +4015,18 @@
       <c r="F25" s="1">
         <v>1</v>
       </c>
-      <c r="G25" s="9"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
+      <c r="G25" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>295</v>
+      </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
@@ -3904,10 +4047,18 @@
       <c r="F26" s="1">
         <v>12</v>
       </c>
-      <c r="G26" s="9"/>
-      <c r="H26" s="9"/>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
+      <c r="G26" s="9">
+        <v>-1519</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
@@ -3928,10 +4079,18 @@
       <c r="F27" s="1">
         <v>6</v>
       </c>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
+      <c r="G27" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
@@ -3952,10 +4111,18 @@
       <c r="F28" s="1">
         <v>3</v>
       </c>
-      <c r="G28" s="9"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
+      <c r="G28" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
@@ -3976,10 +4143,18 @@
       <c r="F29" s="1">
         <v>1</v>
       </c>
-      <c r="G29" s="9"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
+      <c r="G29" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>307</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/graficos_tabelas/preliminares/Tabela_resumo_thetas.xlsx
+++ b/graficos_tabelas/preliminares/Tabela_resumo_thetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6e8fc6e241c731ae/UFABC/Dissertação/volatilidade-IBOV-GPR/Impacto-geopolitico-ibovespa/graficos_tabelas/preliminares/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="713" documentId="11_F25DC773A252ABDACC1048C0F11B46C65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D66360B2-ED2D-400F-8760-1D3321899FE1}"/>
+  <xr:revisionPtr revIDLastSave="733" documentId="11_F25DC773A252ABDACC1048C0F11B46C65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DF6CF67-1D4A-4C76-8214-2BB80FD9C855}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="316">
   <si>
     <t>Garch-Midas nos retornos do Ibovespa</t>
   </si>
@@ -111,9 +111,6 @@
     <t>-0.002</t>
   </si>
   <si>
-    <t>Não estacionário</t>
-  </si>
-  <si>
     <t>Estacionário</t>
   </si>
   <si>
@@ -952,6 +949,33 @@
   </si>
   <si>
     <t>0.063</t>
+  </si>
+  <si>
+    <t>0.404</t>
+  </si>
+  <si>
+    <t>0.275</t>
+  </si>
+  <si>
+    <t>0.500</t>
+  </si>
+  <si>
+    <t>-0.0035</t>
+  </si>
+  <si>
+    <t>0.202</t>
+  </si>
+  <si>
+    <t>-0.0046</t>
+  </si>
+  <si>
+    <t>0.082</t>
+  </si>
+  <si>
+    <t>-0.0013</t>
+  </si>
+  <si>
+    <t>0.226</t>
   </si>
 </sst>
 </file>
@@ -1348,7 +1372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -1498,7 +1522,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -1532,345 +1556,336 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>166</v>
+        <v>310</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>311</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>168</v>
+        <v>312</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>313</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>169</v>
+        <v>314</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>170</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="F15" s="1" t="s">
+      <c r="E16" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="G15" s="5" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>4</v>
-      </c>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="1">
-        <v>0</v>
+        <v>24</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>2</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F19" s="1">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="J19" t="s">
-        <v>56</v>
-      </c>
-      <c r="K19" t="s">
-        <v>57</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>35</v>
+        <v>5</v>
+      </c>
+      <c r="B20" s="1">
+        <v>0</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>179</v>
+        <v>307</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>37</v>
+        <v>26</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="H20" t="s">
-        <v>28</v>
-      </c>
-      <c r="J20" t="s">
-        <v>56</v>
-      </c>
-      <c r="K20" t="s">
-        <v>58</v>
+        <v>309</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>172</v>
+        <v>35</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>179</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="H21" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="J21" t="s">
+        <v>55</v>
+      </c>
+      <c r="K21" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="H22" t="s">
+        <v>27</v>
+      </c>
+      <c r="J22" t="s">
+        <v>55</v>
+      </c>
+      <c r="K22" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G22" s="3" t="s">
+      <c r="G23" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-    </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="K25" t="s">
-        <v>84</v>
-      </c>
+      <c r="A25" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="1">
-        <v>12</v>
+        <v>72</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K26" t="s">
         <v>83</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" s="1">
-        <v>12</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C27" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F27" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>90</v>
+        <v>84</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F28" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>94</v>
+        <v>88</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>6</v>
@@ -1879,126 +1894,126 @@
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F29" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="1">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F30" s="1">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C31" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F31" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C32" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F32" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="J32" s="5" t="s">
-        <v>112</v>
+        <v>106</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>6</v>
@@ -2007,126 +2022,126 @@
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F33" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
+      </c>
+      <c r="J33" s="5" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34" s="1">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F34" s="1">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>120</v>
+        <v>113</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F35" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E36" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F36" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>96</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
@@ -2135,126 +2150,126 @@
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>6</v>
       </c>
       <c r="F37" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>131</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="1">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F38" s="1">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>101</v>
+        <v>130</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C39" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F39" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>138</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F40" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>142</v>
+        <v>135</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>7</v>
@@ -2263,32 +2278,64 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E41" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F41" s="1">
+        <v>3</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="1">
+        <v>3</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F42" s="1">
         <v>1</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G42" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H42" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="I42" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="H41" s="5" t="s">
+      <c r="J42" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>146</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A17:G17"/>
-    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A25:J25"/>
     <mergeCell ref="A12:G12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2308,22 +2355,22 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
@@ -2357,22 +2404,22 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>16</v>
@@ -2380,22 +2427,22 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>16</v>
@@ -2403,7 +2450,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -2437,53 +2484,53 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="G12" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="F13" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -2517,22 +2564,22 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>10</v>
@@ -2540,7 +2587,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B19" s="4">
         <v>-1190</v>
@@ -2549,13 +2596,13 @@
         <v>16</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>16</v>
@@ -2563,7 +2610,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -2597,22 +2644,22 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>16</v>
@@ -2620,22 +2667,22 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>16</v>
@@ -2671,7 +2718,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -2705,53 +2752,53 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="G3" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="F4" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2785,7 +2832,7 @@
         <v>4</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>4</v>
@@ -2793,36 +2840,36 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="H8" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -2835,7 +2882,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -2849,39 +2896,39 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F13" s="1" t="s">
+      <c r="H13" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H13" s="1" t="s">
+      <c r="J13" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>6</v>
@@ -2890,7 +2937,7 @@
         <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>6</v>
@@ -2899,21 +2946,21 @@
         <v>12</v>
       </c>
       <c r="G14" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>162</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>6</v>
@@ -2922,7 +2969,7 @@
         <v>6</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>6</v>
@@ -2931,21 +2978,21 @@
         <v>6</v>
       </c>
       <c r="G15" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="I15" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="H15" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>183</v>
-      </c>
       <c r="J15" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>6</v>
@@ -2954,7 +3001,7 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>6</v>
@@ -2963,21 +3010,21 @@
         <v>3</v>
       </c>
       <c r="G16" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="I16" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="J16" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>6</v>
@@ -2986,7 +3033,7 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>6</v>
@@ -2995,21 +3042,21 @@
         <v>1</v>
       </c>
       <c r="G17" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>6</v>
@@ -3018,7 +3065,7 @@
         <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>7</v>
@@ -3027,21 +3074,21 @@
         <v>12</v>
       </c>
       <c r="G18" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="I18" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="J18" s="5" t="s">
         <v>194</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>6</v>
@@ -3050,7 +3097,7 @@
         <v>6</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>7</v>
@@ -3059,21 +3106,21 @@
         <v>6</v>
       </c>
       <c r="G19" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="H19" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="I19" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="J19" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>6</v>
@@ -3082,7 +3129,7 @@
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>7</v>
@@ -3091,21 +3138,21 @@
         <v>3</v>
       </c>
       <c r="G20" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="I20" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="J20" s="5" t="s">
         <v>202</v>
-      </c>
-      <c r="J20" s="5" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>6</v>
@@ -3114,7 +3161,7 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>7</v>
@@ -3123,21 +3170,21 @@
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I21" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I21" s="1" t="s">
+      <c r="J21" s="3" t="s">
         <v>205</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
@@ -3146,7 +3193,7 @@
         <v>12</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>6</v>
@@ -3155,21 +3202,21 @@
         <v>12</v>
       </c>
       <c r="G22" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="J22" s="1" t="s">
         <v>214</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
@@ -3178,7 +3225,7 @@
         <v>6</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>6</v>
@@ -3187,21 +3234,21 @@
         <v>6</v>
       </c>
       <c r="G23" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="J23" s="1" t="s">
         <v>218</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
@@ -3210,7 +3257,7 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>6</v>
@@ -3219,21 +3266,21 @@
         <v>3</v>
       </c>
       <c r="G24" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="I24" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="J24" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
@@ -3242,7 +3289,7 @@
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>6</v>
@@ -3251,21 +3298,21 @@
         <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="I25" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="I25" s="1" t="s">
-        <v>226</v>
-      </c>
       <c r="J25" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
@@ -3274,7 +3321,7 @@
         <v>12</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>7</v>
@@ -3283,21 +3330,21 @@
         <v>12</v>
       </c>
       <c r="G26" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="I26" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="J26" s="5" t="s">
         <v>229</v>
-      </c>
-      <c r="J26" s="5" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
@@ -3306,7 +3353,7 @@
         <v>6</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>7</v>
@@ -3315,21 +3362,21 @@
         <v>6</v>
       </c>
       <c r="G27" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="H27" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="I27" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="J27" s="3" t="s">
         <v>233</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
@@ -3338,7 +3385,7 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>7</v>
@@ -3347,21 +3394,21 @@
         <v>3</v>
       </c>
       <c r="G28" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="H28" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="I28" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="J28" s="5" t="s">
         <v>237</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
@@ -3370,7 +3417,7 @@
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>7</v>
@@ -3379,16 +3426,16 @@
         <v>1</v>
       </c>
       <c r="G29" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="I29" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="J29" s="5" t="s">
         <v>241</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -3420,7 +3467,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3454,22 +3501,22 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>10</v>
@@ -3477,7 +3524,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B4" s="4">
         <v>-1190</v>
@@ -3486,13 +3533,13 @@
         <v>16</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>16</v>
@@ -3500,7 +3547,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -3534,7 +3581,7 @@
         <v>4</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>4</v>
@@ -3542,65 +3589,65 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="G9" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="H9" s="1" t="s">
+      <c r="I9" s="5" t="s">
         <v>255</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -3614,39 +3661,39 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="F13" s="1" t="s">
+      <c r="H13" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="G13" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H13" s="1" t="s">
+      <c r="J13" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>6</v>
@@ -3655,7 +3702,7 @@
         <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>6</v>
@@ -3664,21 +3711,21 @@
         <v>12</v>
       </c>
       <c r="G14" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="I14" s="1" t="s">
-        <v>259</v>
-      </c>
       <c r="J14" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>6</v>
@@ -3687,7 +3734,7 @@
         <v>6</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>6</v>
@@ -3696,21 +3743,21 @@
         <v>6</v>
       </c>
       <c r="G15" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="I15" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="J15" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>6</v>
@@ -3719,7 +3766,7 @@
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>6</v>
@@ -3728,21 +3775,21 @@
         <v>3</v>
       </c>
       <c r="G16" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="H16" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="I16" s="1" t="s">
+      <c r="J16" s="5" t="s">
         <v>265</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>6</v>
@@ -3751,7 +3798,7 @@
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>6</v>
@@ -3760,21 +3807,21 @@
         <v>1</v>
       </c>
       <c r="G17" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="I17" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="5" t="s">
         <v>269</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>6</v>
@@ -3783,7 +3830,7 @@
         <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>7</v>
@@ -3792,21 +3839,21 @@
         <v>12</v>
       </c>
       <c r="G18" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I18" s="1" t="s">
+      <c r="J18" s="5" t="s">
         <v>272</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>6</v>
@@ -3815,7 +3862,7 @@
         <v>6</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>7</v>
@@ -3824,21 +3871,21 @@
         <v>6</v>
       </c>
       <c r="G19" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="I19" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="I19" s="1" t="s">
+      <c r="J19" s="1" t="s">
         <v>275</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>6</v>
@@ -3847,7 +3894,7 @@
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>7</v>
@@ -3856,21 +3903,21 @@
         <v>3</v>
       </c>
       <c r="G20" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I20" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>278</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>6</v>
@@ -3879,7 +3926,7 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>7</v>
@@ -3888,21 +3935,21 @@
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="I21" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="J21" s="5" t="s">
         <v>281</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
@@ -3911,7 +3958,7 @@
         <v>12</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>6</v>
@@ -3923,18 +3970,18 @@
         <v>-1339</v>
       </c>
       <c r="H22" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="J22" s="5" t="s">
         <v>284</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
@@ -3943,7 +3990,7 @@
         <v>6</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>6</v>
@@ -3952,21 +3999,21 @@
         <v>6</v>
       </c>
       <c r="G23" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="J23" s="3" t="s">
         <v>288</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
@@ -3975,7 +4022,7 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>6</v>
@@ -3984,21 +4031,21 @@
         <v>3</v>
       </c>
       <c r="G24" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="I24" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="I24" s="1" t="s">
-        <v>292</v>
-      </c>
       <c r="J24" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
@@ -4007,7 +4054,7 @@
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E25" s="1" t="s">
         <v>6</v>
@@ -4016,21 +4063,21 @@
         <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="I25" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="J25" s="3" t="s">
         <v>294</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
@@ -4039,7 +4086,7 @@
         <v>12</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>7</v>
@@ -4051,18 +4098,18 @@
         <v>-1519</v>
       </c>
       <c r="H26" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I26" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="I26" s="1" t="s">
-        <v>297</v>
-      </c>
       <c r="J26" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
@@ -4071,7 +4118,7 @@
         <v>6</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>7</v>
@@ -4080,21 +4127,21 @@
         <v>6</v>
       </c>
       <c r="G27" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="I27" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="H27" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="I27" s="1" t="s">
+      <c r="J27" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
@@ -4103,7 +4150,7 @@
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>7</v>
@@ -4112,21 +4159,21 @@
         <v>3</v>
       </c>
       <c r="G28" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="H28" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="I28" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="I28" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="J28" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
@@ -4135,7 +4182,7 @@
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E29" s="1" t="s">
         <v>7</v>
@@ -4144,16 +4191,16 @@
         <v>1</v>
       </c>
       <c r="G29" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="I29" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="J29" s="5" t="s">
         <v>306</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>307</v>
       </c>
     </row>
   </sheetData>

--- a/graficos_tabelas/preliminares/Tabela_resumo_thetas.xlsx
+++ b/graficos_tabelas/preliminares/Tabela_resumo_thetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6e8fc6e241c731ae/UFABC/Dissertação/volatilidade-IBOV-GPR/Impacto-geopolitico-ibovespa/graficos_tabelas/preliminares/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="733" documentId="11_F25DC773A252ABDACC1048C0F11B46C65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DF6CF67-1D4A-4C76-8214-2BB80FD9C855}"/>
+  <xr:revisionPtr revIDLastSave="741" documentId="11_F25DC773A252ABDACC1048C0F11B46C65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA90C009-D415-4793-97EE-E54441718FA4}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="320">
   <si>
     <t>Garch-Midas nos retornos do Ibovespa</t>
   </si>
@@ -976,6 +976,18 @@
   </si>
   <si>
     <t>0.226</t>
+  </si>
+  <si>
+    <t>0.354</t>
+  </si>
+  <si>
+    <t>0.372</t>
+  </si>
+  <si>
+    <t>0.542</t>
+  </si>
+  <si>
+    <t>LOG-DIFF (CAMBIO)</t>
   </si>
 </sst>
 </file>
@@ -1076,6 +1088,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1084,9 +1099,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1403,15 +1415,15 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -1521,15 +1533,15 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -1624,15 +1636,15 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="6"/>
-      <c r="C18" s="6"/>
-      <c r="D18" s="6"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
@@ -1771,18 +1783,18 @@
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="7"/>
+      <c r="J25" s="7"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
@@ -2369,15 +2381,15 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -2449,15 +2461,15 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -2529,15 +2541,15 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="6"/>
-      <c r="E16" s="6"/>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -2570,19 +2582,19 @@
         <v>48</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>10</v>
+        <v>167</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>49</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>10</v>
+        <v>257</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>51</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>10</v>
+        <v>294</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2593,31 +2605,31 @@
         <v>-1190</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>16</v>
+        <v>316</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>67</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>16</v>
+        <v>317</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>16</v>
+        <v>318</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -2717,15 +2729,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -2797,17 +2809,17 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -2869,7 +2881,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>149</v>
+        <v>319</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -2881,18 +2893,18 @@
       <c r="I9" s="1"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -3466,15 +3478,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3507,19 +3519,19 @@
         <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>10</v>
+        <v>167</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>49</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>10</v>
+        <v>257</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>51</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>10</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -3530,33 +3542,33 @@
         <v>-1190</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>316</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>67</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
+        <v>317</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>16</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -3646,18 +3658,18 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -3966,7 +3978,7 @@
       <c r="F22" s="1">
         <v>12</v>
       </c>
-      <c r="G22" s="9">
+      <c r="G22" s="6">
         <v>-1339</v>
       </c>
       <c r="H22" s="1" t="s">
@@ -4094,7 +4106,7 @@
       <c r="F26" s="1">
         <v>12</v>
       </c>
-      <c r="G26" s="9">
+      <c r="G26" s="6">
         <v>-1519</v>
       </c>
       <c r="H26" s="1" t="s">

--- a/graficos_tabelas/preliminares/Tabela_resumo_thetas.xlsx
+++ b/graficos_tabelas/preliminares/Tabela_resumo_thetas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6e8fc6e241c731ae/UFABC/Dissertação/volatilidade-IBOV-GPR/Impacto-geopolitico-ibovespa/graficos_tabelas/preliminares/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="741" documentId="11_F25DC773A252ABDACC1048C0F11B46C65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA90C009-D415-4793-97EE-E54441718FA4}"/>
+  <xr:revisionPtr revIDLastSave="787" documentId="11_F25DC773A252ABDACC1048C0F11B46C65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90AA1FBB-EFAC-4F11-B94B-4035D3D7F81C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IBOV" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="333">
   <si>
     <t>Garch-Midas nos retornos do Ibovespa</t>
   </si>
@@ -988,6 +988,45 @@
   </si>
   <si>
     <t>LOG-DIFF (CAMBIO)</t>
+  </si>
+  <si>
+    <t>-18.33</t>
+  </si>
+  <si>
+    <t>0.058</t>
+  </si>
+  <si>
+    <t>-18.43</t>
+  </si>
+  <si>
+    <t>-0.3569</t>
+  </si>
+  <si>
+    <t>-0.2877</t>
+  </si>
+  <si>
+    <t>VARIANCIA DO CAMBIO X IBOV (SIMÉTRICO)</t>
+  </si>
+  <si>
+    <t>Assimetrico não muda tanto os resultados</t>
+  </si>
+  <si>
+    <t>0.041</t>
+  </si>
+  <si>
+    <t>-0.2468</t>
+  </si>
+  <si>
+    <t>-0.5875</t>
+  </si>
+  <si>
+    <t>-0.2549</t>
+  </si>
+  <si>
+    <t>-0.1222</t>
+  </si>
+  <si>
+    <t>0.164</t>
   </si>
 </sst>
 </file>
@@ -1081,7 +1120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1100,6 +1139,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1384,7 +1425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -1782,9 +1823,18 @@
         <v>10</v>
       </c>
     </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="11"/>
+    </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>96</v>
+        <v>325</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -1792,235 +1842,149 @@
       <c r="E25" s="7"/>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>74</v>
+        <v>4</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>76</v>
+        <v>3</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="K26" t="s">
-        <v>83</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="1">
-        <v>12</v>
+        <v>5</v>
+      </c>
+      <c r="B27" s="1">
+        <v>-101.75</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>288</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" s="1">
-        <v>12</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J27" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>87</v>
+      </c>
+      <c r="H27" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>81</v>
+        <v>6</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="1">
-        <v>6</v>
+        <v>324</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>327</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" s="1">
-        <v>6</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>91</v>
+        <v>323</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>81</v>
+        <v>7</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="1">
-        <v>3</v>
+        <v>329</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>167</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" s="1">
-        <v>3</v>
+        <v>330</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>331</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="1">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" s="1">
-        <v>1</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>100</v>
+        <v>332</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="1">
-        <v>12</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" s="1">
-        <v>12</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>100</v>
-      </c>
+      <c r="A31" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B31" s="7"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="7"/>
+      <c r="J31" s="7"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="1">
-        <v>6</v>
+        <v>72</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" s="1">
-        <v>6</v>
+        <v>72</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>107</v>
+        <v>78</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K32" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -2031,28 +1995,28 @@
         <v>6</v>
       </c>
       <c r="C33" s="1">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>82</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F33" s="1">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>110</v>
+        <v>86</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="J33" s="5" t="s">
-        <v>111</v>
+        <v>85</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -2063,28 +2027,28 @@
         <v>6</v>
       </c>
       <c r="C34" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>82</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F34" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>114</v>
+        <v>88</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>89</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>115</v>
+        <v>90</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -2092,10 +2056,10 @@
         <v>81</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35" s="1">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>82</v>
@@ -2104,19 +2068,19 @@
         <v>6</v>
       </c>
       <c r="F35" s="1">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -2124,10 +2088,10 @@
         <v>81</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C36" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>82</v>
@@ -2136,19 +2100,19 @@
         <v>6</v>
       </c>
       <c r="F36" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
@@ -2156,31 +2120,31 @@
         <v>81</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C37" s="1">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>82</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F37" s="1">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
@@ -2188,31 +2152,31 @@
         <v>81</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C38" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>82</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F38" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>127</v>
+        <v>104</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
@@ -2220,10 +2184,10 @@
         <v>81</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C39" s="1">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>82</v>
@@ -2232,19 +2196,19 @@
         <v>7</v>
       </c>
       <c r="F39" s="1">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>100</v>
+        <v>109</v>
+      </c>
+      <c r="J39" s="5" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
@@ -2252,10 +2216,10 @@
         <v>81</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C40" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>82</v>
@@ -2264,19 +2228,19 @@
         <v>7</v>
       </c>
       <c r="F40" s="1">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>137</v>
+        <v>113</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
@@ -2287,28 +2251,28 @@
         <v>7</v>
       </c>
       <c r="C41" s="1">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>82</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F41" s="1">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>141</v>
+        <v>117</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
@@ -2319,36 +2283,229 @@
         <v>7</v>
       </c>
       <c r="C42" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>82</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F42" s="1">
+        <v>6</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="1">
+        <v>3</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F43" s="1">
+        <v>3</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="1">
+        <v>3</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F44" s="1">
         <v>1</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G44" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="1">
+        <v>12</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F45" s="1">
+        <v>12</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="1">
+        <v>6</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F46" s="1">
+        <v>6</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="1">
+        <v>3</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F47" s="1">
+        <v>3</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="1">
+        <v>3</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F48" s="1">
+        <v>1</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="H42" s="5" t="s">
+      <c r="H48" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="I42" s="1" t="s">
+      <c r="I48" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="J42" s="1" t="s">
+      <c r="J48" s="1" t="s">
         <v>145</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="A31:J31"/>
     <mergeCell ref="A12:G12"/>
+    <mergeCell ref="A25:G25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/graficos_tabelas/preliminares/Tabela_resumo_thetas.xlsx
+++ b/graficos_tabelas/preliminares/Tabela_resumo_thetas.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6e8fc6e241c731ae/UFABC/Dissertação/volatilidade-IBOV-GPR/Impacto-geopolitico-ibovespa/graficos_tabelas/preliminares/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="787" documentId="11_F25DC773A252ABDACC1048C0F11B46C65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90AA1FBB-EFAC-4F11-B94B-4035D3D7F81C}"/>
+  <xr:revisionPtr revIDLastSave="932" documentId="11_F25DC773A252ABDACC1048C0F11B46C65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D6888D5-6D66-4EE8-B89A-36D3F6D52FBD}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IBOV" sheetId="1" r:id="rId1"/>
     <sheet name="SETORES" sheetId="2" r:id="rId2"/>
     <sheet name="CONSUMO" sheetId="3" r:id="rId3"/>
     <sheet name="BENS BASICOS" sheetId="4" r:id="rId4"/>
+    <sheet name="FINANCEIRO" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="424">
   <si>
     <t>Garch-Midas nos retornos do Ibovespa</t>
   </si>
@@ -756,9 +757,6 @@
     <t>0.066</t>
   </si>
   <si>
-    <t>SETOR BENS BASICOS X CAMBIO</t>
-  </si>
-  <si>
     <t>MODELO 2 - GPR GLOBAL E VAR CAMBIO ASSIMÉTRICO - SETOR: BENS BASICOS</t>
   </si>
   <si>
@@ -1027,6 +1025,282 @@
   </si>
   <si>
     <t>0.164</t>
+  </si>
+  <si>
+    <t>MODELO 2 - GPR GLOBAL E VAR CAMBIO ASSIMÉTRICO - SETOR: FINANCEIRO</t>
+  </si>
+  <si>
+    <t>SETOR FINANCEIRO X CAMBIO (ASSIMETRICO)</t>
+  </si>
+  <si>
+    <t>SETOR BENS BASICOS X CAMBIO (ASSIMÉTRICO)</t>
+  </si>
+  <si>
+    <t>-0.1206</t>
+  </si>
+  <si>
+    <t>0.311</t>
+  </si>
+  <si>
+    <t>-0.1283</t>
+  </si>
+  <si>
+    <t>0.280</t>
+  </si>
+  <si>
+    <t>-0.1393</t>
+  </si>
+  <si>
+    <t>0.138</t>
+  </si>
+  <si>
+    <t>-0.0652</t>
+  </si>
+  <si>
+    <t>0.132</t>
+  </si>
+  <si>
+    <t>-0.4144</t>
+  </si>
+  <si>
+    <t>0.108</t>
+  </si>
+  <si>
+    <t>-0.2075</t>
+  </si>
+  <si>
+    <t>0.160</t>
+  </si>
+  <si>
+    <t>-0.0427</t>
+  </si>
+  <si>
+    <t>0.235</t>
+  </si>
+  <si>
+    <t>-0.0283</t>
+  </si>
+  <si>
+    <t>0.337</t>
+  </si>
+  <si>
+    <t>BIC</t>
+  </si>
+  <si>
+    <t>-0.1468</t>
+  </si>
+  <si>
+    <t>0.547</t>
+  </si>
+  <si>
+    <t>-0.1248</t>
+  </si>
+  <si>
+    <t>0.248</t>
+  </si>
+  <si>
+    <t>24331.27</t>
+  </si>
+  <si>
+    <t>-0.1892</t>
+  </si>
+  <si>
+    <t>0.536</t>
+  </si>
+  <si>
+    <t>-0.1065</t>
+  </si>
+  <si>
+    <t>0.509</t>
+  </si>
+  <si>
+    <t>24841.36</t>
+  </si>
+  <si>
+    <t>-0.1599</t>
+  </si>
+  <si>
+    <t>0.553</t>
+  </si>
+  <si>
+    <t>0.094</t>
+  </si>
+  <si>
+    <t>25115.43</t>
+  </si>
+  <si>
+    <t>-0.0790</t>
+  </si>
+  <si>
+    <t>0.341</t>
+  </si>
+  <si>
+    <t>-0.0519</t>
+  </si>
+  <si>
+    <t>0.232</t>
+  </si>
+  <si>
+    <t>25108.41</t>
+  </si>
+  <si>
+    <t>-0.1546</t>
+  </si>
+  <si>
+    <t>0.514</t>
+  </si>
+  <si>
+    <t>-0.4642</t>
+  </si>
+  <si>
+    <t>24329.44</t>
+  </si>
+  <si>
+    <t>-0.1680</t>
+  </si>
+  <si>
+    <t>0.836</t>
+  </si>
+  <si>
+    <t>-0.2073</t>
+  </si>
+  <si>
+    <t>24841.1</t>
+  </si>
+  <si>
+    <t>0.645</t>
+  </si>
+  <si>
+    <t>-0.0371</t>
+  </si>
+  <si>
+    <t>0.253</t>
+  </si>
+  <si>
+    <t>25119.4</t>
+  </si>
+  <si>
+    <t>-0.1956</t>
+  </si>
+  <si>
+    <t>0.639</t>
+  </si>
+  <si>
+    <t>-0.0340</t>
+  </si>
+  <si>
+    <t>0.251</t>
+  </si>
+  <si>
+    <t>25108.7</t>
+  </si>
+  <si>
+    <t>0.1492</t>
+  </si>
+  <si>
+    <t>0.671</t>
+  </si>
+  <si>
+    <t>-0.1359</t>
+  </si>
+  <si>
+    <t>0.237</t>
+  </si>
+  <si>
+    <t>24331.58</t>
+  </si>
+  <si>
+    <t>0.1162</t>
+  </si>
+  <si>
+    <t>0.617</t>
+  </si>
+  <si>
+    <t>-0.1350</t>
+  </si>
+  <si>
+    <t>0.250</t>
+  </si>
+  <si>
+    <t>24842.34</t>
+  </si>
+  <si>
+    <t>0.0777</t>
+  </si>
+  <si>
+    <t>0.527</t>
+  </si>
+  <si>
+    <t>-0.1325</t>
+  </si>
+  <si>
+    <t>25116.43</t>
+  </si>
+  <si>
+    <t>0.0522</t>
+  </si>
+  <si>
+    <t>0.555</t>
+  </si>
+  <si>
+    <t>-0.0650</t>
+  </si>
+  <si>
+    <t>0.140</t>
+  </si>
+  <si>
+    <t>25109.09</t>
+  </si>
+  <si>
+    <t>0.1769</t>
+  </si>
+  <si>
+    <t>0.614</t>
+  </si>
+  <si>
+    <t>-0.4361</t>
+  </si>
+  <si>
+    <t>0.098</t>
+  </si>
+  <si>
+    <t>24330.03</t>
+  </si>
+  <si>
+    <t>0.1154</t>
+  </si>
+  <si>
+    <t>0.630</t>
+  </si>
+  <si>
+    <t>-0.2008</t>
+  </si>
+  <si>
+    <t>24842.24</t>
+  </si>
+  <si>
+    <t>0.1976</t>
+  </si>
+  <si>
+    <t>-0.0386</t>
+  </si>
+  <si>
+    <t>0.228</t>
+  </si>
+  <si>
+    <t>25118.81</t>
+  </si>
+  <si>
+    <t>0.1469</t>
+  </si>
+  <si>
+    <t>0.998</t>
+  </si>
+  <si>
+    <t>-0.0354</t>
+  </si>
+  <si>
+    <t>0.957</t>
   </si>
 </sst>
 </file>
@@ -1139,8 +1413,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1612,22 +1888,22 @@
         <v>5</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="F14" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="G14" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -1718,19 +1994,19 @@
         <v>0</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F20" s="1">
         <v>0</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>27</v>
@@ -1823,18 +2099,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="11"/>
-    </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -1874,22 +2141,22 @@
         <v>-101.75</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D27" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="F27" s="1" t="s">
         <v>321</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>322</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>87</v>
       </c>
       <c r="H27" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1897,19 +2164,19 @@
         <v>6</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>167</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>95</v>
@@ -1920,22 +2187,22 @@
         <v>7</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>167</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>196</v>
       </c>
       <c r="F29" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -2745,13 +3012,13 @@
         <v>49</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>51</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -2762,19 +3029,19 @@
         <v>-1190</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>67</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -3038,7 +3305,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -3682,13 +3949,13 @@
         <v>49</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>51</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -3699,33 +3966,33 @@
         <v>-1190</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>67</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>68</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>242</v>
-      </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
+      <c r="A6" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -3761,19 +4028,19 @@
         <v>148</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="1" t="s">
         <v>247</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>248</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>107</v>
@@ -3782,7 +4049,7 @@
         <v>221</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -3790,33 +4057,33 @@
         <v>149</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>165</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>253</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>100</v>
       </c>
       <c r="H9" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>254</v>
-      </c>
-      <c r="I9" s="5" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -3880,13 +4147,13 @@
         <v>12</v>
       </c>
       <c r="G14" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="H14" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>258</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>167</v>
@@ -3912,16 +4179,16 @@
         <v>6</v>
       </c>
       <c r="G15" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="H15" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="I15" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="J15" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -3944,16 +4211,16 @@
         <v>3</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>196</v>
       </c>
       <c r="I16" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="J16" s="5" t="s">
         <v>264</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -3976,16 +4243,16 @@
         <v>1</v>
       </c>
       <c r="G17" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="I17" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="5" t="s">
         <v>268</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
@@ -4008,16 +4275,16 @@
         <v>12</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>119</v>
       </c>
       <c r="I18" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="J18" s="5" t="s">
         <v>271</v>
-      </c>
-      <c r="J18" s="5" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -4040,16 +4307,16 @@
         <v>6</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>100</v>
       </c>
       <c r="I19" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="J19" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -4072,13 +4339,13 @@
         <v>3</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>198</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>100</v>
@@ -4104,16 +4371,16 @@
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="H21" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="I21" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="J21" s="5" t="s">
         <v>280</v>
-      </c>
-      <c r="J21" s="5" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -4139,13 +4406,13 @@
         <v>-1339</v>
       </c>
       <c r="H22" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I22" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="J22" s="5" t="s">
         <v>283</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -4168,16 +4435,16 @@
         <v>6</v>
       </c>
       <c r="G23" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="J23" s="3" t="s">
         <v>287</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -4200,13 +4467,13 @@
         <v>3</v>
       </c>
       <c r="G24" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="I24" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>291</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>137</v>
@@ -4232,16 +4499,16 @@
         <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>292</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>293</v>
       </c>
       <c r="I25" s="1" t="s">
         <v>97</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -4267,10 +4534,10 @@
         <v>-1519</v>
       </c>
       <c r="H26" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="I26" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>296</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>111</v>
@@ -4296,16 +4563,16 @@
         <v>6</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>173</v>
       </c>
       <c r="I27" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="J27" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -4328,16 +4595,16 @@
         <v>3</v>
       </c>
       <c r="G28" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="H28" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="I28" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="I28" s="1" t="s">
-        <v>302</v>
-      </c>
       <c r="J28" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -4360,16 +4627,16 @@
         <v>1</v>
       </c>
       <c r="G29" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="I29" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="J29" s="5" t="s">
         <v>305</v>
-      </c>
-      <c r="J29" s="5" t="s">
-        <v>306</v>
       </c>
     </row>
   </sheetData>
@@ -4380,4 +4647,820 @@
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA68D41D-10F9-466A-B0F2-E9697587C33C}">
+  <dimension ref="A1:K29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>349</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K13" s="10" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="1">
+        <v>12</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="1">
+        <v>12</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="1">
+        <v>6</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" s="1">
+        <v>6</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="1">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" s="1">
+        <v>3</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="J16" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="1">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="1">
+        <v>12</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" s="1">
+        <v>12</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="J18" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="1">
+        <v>6</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" s="1">
+        <v>6</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="1">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" s="1">
+        <v>3</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="1">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>385</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="1">
+        <v>12</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="1">
+        <v>12</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>388</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="1">
+        <v>6</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" s="1">
+        <v>6</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="1">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" s="1">
+        <v>3</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="1">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="1">
+        <v>12</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" s="1">
+        <v>12</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>407</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="1">
+        <v>6</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" s="1">
+        <v>6</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="1">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" s="1">
+        <v>3</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>417</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="1">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" s="1">
+        <v>1</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="K29" s="1">
+        <v>25110</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A12:K12"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/graficos_tabelas/preliminares/Tabela_resumo_thetas.xlsx
+++ b/graficos_tabelas/preliminares/Tabela_resumo_thetas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6e8fc6e241c731ae/UFABC/Dissertação/volatilidade-IBOV-GPR/Impacto-geopolitico-ibovespa/graficos_tabelas/preliminares/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="932" documentId="11_F25DC773A252ABDACC1048C0F11B46C65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D6888D5-6D66-4EE8-B89A-36D3F6D52FBD}"/>
+  <xr:revisionPtr revIDLastSave="1073" documentId="11_F25DC773A252ABDACC1048C0F11B46C65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B58D5D75-4918-415F-9C4C-B32340697E2D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IBOV" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="CONSUMO" sheetId="3" r:id="rId3"/>
     <sheet name="BENS BASICOS" sheetId="4" r:id="rId4"/>
     <sheet name="FINANCEIRO" sheetId="5" r:id="rId5"/>
+    <sheet name="ENERGIA" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="936" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="483">
   <si>
     <t>Garch-Midas nos retornos do Ibovespa</t>
   </si>
@@ -1301,6 +1302,183 @@
   </si>
   <si>
     <t>0.957</t>
+  </si>
+  <si>
+    <t>SETOR DE ENERGIA X CAMBIO (ASSIMETRICO)</t>
+  </si>
+  <si>
+    <t>0.1680</t>
+  </si>
+  <si>
+    <t>0.193</t>
+  </si>
+  <si>
+    <t>-0.0881</t>
+  </si>
+  <si>
+    <t>0.310</t>
+  </si>
+  <si>
+    <t>-0.1370</t>
+  </si>
+  <si>
+    <t>-0.0983</t>
+  </si>
+  <si>
+    <t>-0.3869</t>
+  </si>
+  <si>
+    <t>-0.3317</t>
+  </si>
+  <si>
+    <t>0.040</t>
+  </si>
+  <si>
+    <t>-0.1931</t>
+  </si>
+  <si>
+    <t>0.042</t>
+  </si>
+  <si>
+    <t>-0.0364</t>
+  </si>
+  <si>
+    <t>0.272</t>
+  </si>
+  <si>
+    <t>IC-BR X IBOV (SIMÉTRICO)</t>
+  </si>
+  <si>
+    <t>-0.0794</t>
+  </si>
+  <si>
+    <t>0.133</t>
+  </si>
+  <si>
+    <t>-0.0297</t>
+  </si>
+  <si>
+    <t>0.229</t>
+  </si>
+  <si>
+    <t>-0.0145</t>
+  </si>
+  <si>
+    <t>0.386</t>
+  </si>
+  <si>
+    <t>MODELO 2 - GPR GLOBAL E IC-BR ASSIMÉTRICO</t>
+  </si>
+  <si>
+    <t>IC-BR</t>
+  </si>
+  <si>
+    <t>-0.1753</t>
+  </si>
+  <si>
+    <t>0.505</t>
+  </si>
+  <si>
+    <t>-0.1027</t>
+  </si>
+  <si>
+    <t>0.038</t>
+  </si>
+  <si>
+    <t>23392.36</t>
+  </si>
+  <si>
+    <t>-0.5413</t>
+  </si>
+  <si>
+    <t>0.061</t>
+  </si>
+  <si>
+    <t>23900.2</t>
+  </si>
+  <si>
+    <t>-0.3052</t>
+  </si>
+  <si>
+    <t>0.409</t>
+  </si>
+  <si>
+    <t>-0.0243</t>
+  </si>
+  <si>
+    <t>0.159</t>
+  </si>
+  <si>
+    <t>24160.61</t>
+  </si>
+  <si>
+    <t>-0.2859</t>
+  </si>
+  <si>
+    <t>0.397</t>
+  </si>
+  <si>
+    <t>-0.0068</t>
+  </si>
+  <si>
+    <t>0.391</t>
+  </si>
+  <si>
+    <t>24154.19</t>
+  </si>
+  <si>
+    <t>-0.2297</t>
+  </si>
+  <si>
+    <t>0.996</t>
+  </si>
+  <si>
+    <t>-0.1044</t>
+  </si>
+  <si>
+    <t>0.586</t>
+  </si>
+  <si>
+    <t>23394.09</t>
+  </si>
+  <si>
+    <t>0.2428</t>
+  </si>
+  <si>
+    <t>0.415</t>
+  </si>
+  <si>
+    <t>-0.0344</t>
+  </si>
+  <si>
+    <t>0.142</t>
+  </si>
+  <si>
+    <t>23906.31</t>
+  </si>
+  <si>
+    <t>0.4224</t>
+  </si>
+  <si>
+    <t>-0.0170</t>
+  </si>
+  <si>
+    <t>0.301</t>
+  </si>
+  <si>
+    <t>24162.68</t>
+  </si>
+  <si>
+    <t>0.4391</t>
+  </si>
+  <si>
+    <t>-0.0053</t>
+  </si>
+  <si>
+    <t>24155.3</t>
+  </si>
+  <si>
+    <t>MODELO 2 - GPR GLOBAL E VAR CAMBIO ASSIMÉTRICO - SETOR: ENERGIA</t>
   </si>
 </sst>
 </file>
@@ -1394,7 +1572,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1404,6 +1582,9 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1412,10 +1593,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1701,7 +1878,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K48"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -1713,7 +1890,8 @@
     <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="99.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.7109375" customWidth="1"/>
+    <col min="12" max="12" width="99.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -1732,15 +1910,15 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -1850,15 +2028,15 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -1952,18 +2130,18 @@
         <v>177</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>24</v>
       </c>
@@ -1986,7 +2164,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>5</v>
       </c>
@@ -2012,7 +2190,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>6</v>
       </c>
@@ -2040,11 +2218,11 @@
       <c r="J21" t="s">
         <v>55</v>
       </c>
-      <c r="K21" t="s">
+      <c r="L21" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>7</v>
       </c>
@@ -2072,11 +2250,11 @@
       <c r="J22" t="s">
         <v>55</v>
       </c>
-      <c r="K22" t="s">
+      <c r="L22" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>8</v>
       </c>
@@ -2099,18 +2277,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
         <v>324</v>
       </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B25" s="8"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="8"/>
+      <c r="E25" s="8"/>
+      <c r="F25" s="8"/>
+      <c r="G25" s="8"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
@@ -2133,7 +2311,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>5</v>
       </c>
@@ -2159,7 +2337,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>6</v>
       </c>
@@ -2182,7 +2360,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>7</v>
       </c>
@@ -2205,21 +2383,22 @@
         <v>331</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="7"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="7"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>73</v>
       </c>
@@ -2250,7 +2429,7 @@
       <c r="J32" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="K32" t="s">
+      <c r="L32" t="s">
         <v>83</v>
       </c>
     </row>
@@ -2766,8 +2945,397 @@
         <v>145</v>
       </c>
     </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="8" t="s">
+        <v>438</v>
+      </c>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="8"/>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="8" t="s">
+        <v>445</v>
+      </c>
+      <c r="B54" s="8"/>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="8"/>
+      <c r="J54" s="8"/>
+      <c r="K54" s="8"/>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I55" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="1">
+        <v>12</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F56" s="1">
+        <v>12</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="1">
+        <v>6</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F57" s="1">
+        <v>6</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J57" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="1">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F58" s="1">
+        <v>3</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="1">
+        <v>3</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F59" s="1">
+        <v>1</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="I59" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="1">
+        <v>12</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F60" s="1">
+        <v>12</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="I60" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="1">
+        <v>6</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F61" s="1">
+        <v>6</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="I61" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="1">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F62" s="1">
+        <v>3</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="1">
+        <v>3</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F63" s="1">
+        <v>1</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>481</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
+    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A54:K54"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A18:G18"/>
     <mergeCell ref="A31:J31"/>
@@ -2805,15 +3373,15 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -2885,15 +3453,15 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -2965,15 +3533,15 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -3045,15 +3613,15 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -3153,15 +3721,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3233,17 +3801,17 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="9"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -3317,18 +3885,18 @@
       <c r="I9" s="1"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -3902,15 +4470,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -3982,17 +4550,17 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="8" t="s">
         <v>334</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -4082,18 +4650,18 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -4666,15 +5234,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4746,17 +5314,17 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="8" t="s">
         <v>333</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -4791,28 +5359,28 @@
       <c r="A8" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="F8" s="10" t="s">
+      <c r="F8" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="1" t="s">
         <v>342</v>
       </c>
     </row>
@@ -4820,45 +5388,45 @@
       <c r="A9" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="1" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -4891,7 +5459,7 @@
       <c r="J13" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="K13" s="10" t="s">
+      <c r="K13" s="1" t="s">
         <v>351</v>
       </c>
     </row>
@@ -4914,19 +5482,19 @@
       <c r="F14" s="1">
         <v>12</v>
       </c>
-      <c r="G14" s="10" t="s">
+      <c r="G14" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="H14" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="I14" s="10" t="s">
+      <c r="I14" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="J14" s="10" t="s">
+      <c r="J14" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="K14" s="10" t="s">
+      <c r="K14" s="1" t="s">
         <v>356</v>
       </c>
     </row>
@@ -4949,16 +5517,16 @@
       <c r="F15" s="1">
         <v>6</v>
       </c>
-      <c r="G15" s="10" t="s">
+      <c r="G15" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="H15" s="10" t="s">
+      <c r="H15" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="I15" s="10" t="s">
+      <c r="I15" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="J15" s="10" t="s">
+      <c r="J15" s="1" t="s">
         <v>360</v>
       </c>
       <c r="K15" s="1" t="s">
@@ -4984,13 +5552,13 @@
       <c r="F16" s="1">
         <v>3</v>
       </c>
-      <c r="G16" s="10" t="s">
+      <c r="G16" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="H16" s="10" t="s">
+      <c r="H16" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="I16" s="10" t="s">
+      <c r="I16" s="1" t="s">
         <v>362</v>
       </c>
       <c r="J16" s="5" t="s">
@@ -5019,16 +5587,16 @@
       <c r="F17" s="1">
         <v>1</v>
       </c>
-      <c r="G17" s="10" t="s">
+      <c r="G17" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="H17" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="I17" s="10" t="s">
+      <c r="I17" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="J17" s="10" t="s">
+      <c r="J17" s="1" t="s">
         <v>369</v>
       </c>
       <c r="K17" s="1" t="s">
@@ -5054,13 +5622,13 @@
       <c r="F18" s="1">
         <v>12</v>
       </c>
-      <c r="G18" s="10" t="s">
+      <c r="G18" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="H18" s="10" t="s">
+      <c r="H18" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="I18" s="10" t="s">
+      <c r="I18" s="1" t="s">
         <v>373</v>
       </c>
       <c r="J18" s="5" t="s">
@@ -5089,16 +5657,16 @@
       <c r="F19" s="1">
         <v>6</v>
       </c>
-      <c r="G19" s="10" t="s">
+      <c r="G19" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="I19" s="10" t="s">
+      <c r="I19" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="J19" s="10" t="s">
+      <c r="J19" s="1" t="s">
         <v>140</v>
       </c>
       <c r="K19" s="1" t="s">
@@ -5124,16 +5692,16 @@
       <c r="F20" s="1">
         <v>3</v>
       </c>
-      <c r="G20" s="10" t="s">
+      <c r="G20" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="H20" s="10" t="s">
+      <c r="H20" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="I20" s="10" t="s">
+      <c r="I20" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="J20" s="10" t="s">
+      <c r="J20" s="1" t="s">
         <v>381</v>
       </c>
       <c r="K20" s="1" t="s">
@@ -5159,16 +5727,16 @@
       <c r="F21" s="1">
         <v>1</v>
       </c>
-      <c r="G21" s="10" t="s">
+      <c r="G21" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="H21" s="10" t="s">
+      <c r="H21" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="I21" s="10" t="s">
+      <c r="I21" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="J21" s="10" t="s">
+      <c r="J21" s="1" t="s">
         <v>386</v>
       </c>
       <c r="K21" s="1" t="s">
@@ -5194,16 +5762,16 @@
       <c r="F22" s="1">
         <v>12</v>
       </c>
-      <c r="G22" s="11" t="s">
+      <c r="G22" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="H22" s="10" t="s">
+      <c r="H22" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="I22" s="10" t="s">
+      <c r="I22" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="J22" s="10" t="s">
+      <c r="J22" s="1" t="s">
         <v>391</v>
       </c>
       <c r="K22" s="1" t="s">
@@ -5229,16 +5797,16 @@
       <c r="F23" s="1">
         <v>6</v>
       </c>
-      <c r="G23" s="10" t="s">
+      <c r="G23" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="H23" s="10" t="s">
+      <c r="H23" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="I23" s="10" t="s">
+      <c r="I23" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="J23" s="10" t="s">
+      <c r="J23" s="1" t="s">
         <v>396</v>
       </c>
       <c r="K23" s="1" t="s">
@@ -5264,16 +5832,16 @@
       <c r="F24" s="1">
         <v>3</v>
       </c>
-      <c r="G24" s="10" t="s">
+      <c r="G24" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="H24" s="10" t="s">
+      <c r="H24" s="1" t="s">
         <v>399</v>
       </c>
-      <c r="I24" s="10" t="s">
+      <c r="I24" s="1" t="s">
         <v>400</v>
       </c>
-      <c r="J24" s="10" t="s">
+      <c r="J24" s="1" t="s">
         <v>105</v>
       </c>
       <c r="K24" s="1" t="s">
@@ -5299,16 +5867,16 @@
       <c r="F25" s="1">
         <v>1</v>
       </c>
-      <c r="G25" s="10" t="s">
+      <c r="G25" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="H25" s="10" t="s">
+      <c r="H25" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="I25" s="10" t="s">
+      <c r="I25" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="J25" s="10" t="s">
+      <c r="J25" s="1" t="s">
         <v>405</v>
       </c>
       <c r="K25" s="1" t="s">
@@ -5334,13 +5902,13 @@
       <c r="F26" s="1">
         <v>12</v>
       </c>
-      <c r="G26" s="11" t="s">
+      <c r="G26" s="6" t="s">
         <v>407</v>
       </c>
-      <c r="H26" s="10" t="s">
+      <c r="H26" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="I26" s="10" t="s">
+      <c r="I26" s="1" t="s">
         <v>409</v>
       </c>
       <c r="J26" s="5" t="s">
@@ -5369,16 +5937,16 @@
       <c r="F27" s="1">
         <v>6</v>
       </c>
-      <c r="G27" s="10" t="s">
+      <c r="G27" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="H27" s="10" t="s">
+      <c r="H27" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="I27" s="10" t="s">
+      <c r="I27" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="J27" s="10" t="s">
+      <c r="J27" s="1" t="s">
         <v>145</v>
       </c>
       <c r="K27" s="1" t="s">
@@ -5404,16 +5972,16 @@
       <c r="F28" s="1">
         <v>3</v>
       </c>
-      <c r="G28" s="10" t="s">
+      <c r="G28" s="1" t="s">
         <v>416</v>
       </c>
-      <c r="H28" s="10" t="s">
+      <c r="H28" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="I28" s="10" t="s">
+      <c r="I28" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="J28" s="10" t="s">
+      <c r="J28" s="1" t="s">
         <v>418</v>
       </c>
       <c r="K28" s="1" t="s">
@@ -5439,16 +6007,16 @@
       <c r="F29" s="1">
         <v>1</v>
       </c>
-      <c r="G29" s="10" t="s">
+      <c r="G29" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="H29" s="10" t="s">
+      <c r="H29" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="I29" s="10" t="s">
+      <c r="I29" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="J29" s="10" t="s">
+      <c r="J29" s="1" t="s">
         <v>423</v>
       </c>
       <c r="K29" s="1">
@@ -5463,4 +6031,819 @@
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8A15EAB-E8AF-4154-BF83-3C8820BC69B3}">
+  <dimension ref="A1:K28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="E1" s="8"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>482</v>
+      </c>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="1">
+        <v>12</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13" s="1">
+        <v>12</v>
+      </c>
+      <c r="G13" s="1">
+        <v>6.8500000000000005E-2</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0.62219999999999998</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0.159</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0.22420000000000001</v>
+      </c>
+      <c r="K13" s="1">
+        <v>24289.2978</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="1">
+        <v>6</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" s="1">
+        <v>6</v>
+      </c>
+      <c r="G14" s="1">
+        <v>-0.22670000000000001</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0.84670000000000001</v>
+      </c>
+      <c r="I14" s="1">
+        <v>-9.69E-2</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0.32250000000000001</v>
+      </c>
+      <c r="K14" s="1">
+        <v>24798.072100000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="1">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" s="1">
+        <v>3</v>
+      </c>
+      <c r="G15" s="1">
+        <v>-9.0700000000000003E-2</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0.50960000000000005</v>
+      </c>
+      <c r="I15" s="1">
+        <v>-0.1159</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0.48049999999999998</v>
+      </c>
+      <c r="K15" s="1">
+        <v>25069.443899999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="1">
+        <v>3</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1</v>
+      </c>
+      <c r="G16" s="1">
+        <v>-9.8500000000000004E-2</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0.54169999999999996</v>
+      </c>
+      <c r="I16" s="1">
+        <v>-9.2700000000000005E-2</v>
+      </c>
+      <c r="J16" s="1">
+        <v>0.14699999999999999</v>
+      </c>
+      <c r="K16" s="1">
+        <v>25060.772799999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="1">
+        <v>12</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F17" s="1">
+        <v>12</v>
+      </c>
+      <c r="G17" s="1">
+        <v>4.1599999999999998E-2</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0.74639999999999995</v>
+      </c>
+      <c r="I17" s="1">
+        <v>-7.9799999999999996E-2</v>
+      </c>
+      <c r="J17" s="1">
+        <v>0.51400000000000001</v>
+      </c>
+      <c r="K17" s="1">
+        <v>24290.551899999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="1">
+        <v>6</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" s="1">
+        <v>6</v>
+      </c>
+      <c r="G18" s="1">
+        <v>-6.8000000000000005E-2</v>
+      </c>
+      <c r="H18" s="1">
+        <v>0.84199999999999997</v>
+      </c>
+      <c r="I18" s="1">
+        <v>-0.1106</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0.25480000000000003</v>
+      </c>
+      <c r="K18" s="1">
+        <v>24800.231</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="1">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" s="1">
+        <v>3</v>
+      </c>
+      <c r="G19" s="1">
+        <v>-0.13039999999999999</v>
+      </c>
+      <c r="H19" s="1">
+        <v>0.42370000000000002</v>
+      </c>
+      <c r="I19" s="1">
+        <v>-0.12540000000000001</v>
+      </c>
+      <c r="J19" s="1">
+        <v>0.28070000000000001</v>
+      </c>
+      <c r="K19" s="1">
+        <v>25068.5471</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="1">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1</v>
+      </c>
+      <c r="G20" s="1">
+        <v>-0.12230000000000001</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0.42280000000000001</v>
+      </c>
+      <c r="I20" s="1">
+        <v>-0.104</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0.1048</v>
+      </c>
+      <c r="K20" s="1">
+        <v>25060.023799999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="1">
+        <v>12</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" s="1">
+        <v>12</v>
+      </c>
+      <c r="G21" s="1">
+        <v>-4.3900000000000002E-2</v>
+      </c>
+      <c r="H21" s="1">
+        <v>0.98629999999999995</v>
+      </c>
+      <c r="I21" s="1">
+        <v>-0.4108</v>
+      </c>
+      <c r="J21" s="5">
+        <v>7.0099999999999996E-2</v>
+      </c>
+      <c r="K21" s="1">
+        <v>24286.004700000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="1">
+        <v>6</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F22" s="1">
+        <v>6</v>
+      </c>
+      <c r="G22" s="1">
+        <v>-0.35339999999999999</v>
+      </c>
+      <c r="H22" s="1">
+        <v>0.20860000000000001</v>
+      </c>
+      <c r="I22" s="1">
+        <v>-0.3281</v>
+      </c>
+      <c r="J22" s="3">
+        <v>4.4400000000000002E-2</v>
+      </c>
+      <c r="K22" s="1">
+        <v>24793.712899999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="1">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F23" s="1">
+        <v>3</v>
+      </c>
+      <c r="G23" s="1">
+        <v>-8.9099999999999999E-2</v>
+      </c>
+      <c r="H23" s="1">
+        <v>0.53149999999999997</v>
+      </c>
+      <c r="I23" s="1">
+        <v>-0.1978</v>
+      </c>
+      <c r="J23" s="3">
+        <v>3.4799999999999998E-2</v>
+      </c>
+      <c r="K23" s="1">
+        <v>25067.946400000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="1">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1</v>
+      </c>
+      <c r="G24" s="1">
+        <v>-0.13270000000000001</v>
+      </c>
+      <c r="H24" s="1">
+        <v>0.32419999999999999</v>
+      </c>
+      <c r="I24" s="1">
+        <v>-3.6799999999999999E-2</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0.27350000000000002</v>
+      </c>
+      <c r="K24" s="1">
+        <v>25063.220700000002</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="1">
+        <v>12</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F25" s="1">
+        <v>12</v>
+      </c>
+      <c r="G25" s="1">
+        <v>-0.17519999999999999</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0.879</v>
+      </c>
+      <c r="I25" s="1">
+        <v>-0.3755</v>
+      </c>
+      <c r="J25" s="5">
+        <v>9.7500000000000003E-2</v>
+      </c>
+      <c r="K25" s="1">
+        <v>24286.143199999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="1">
+        <v>6</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" s="1">
+        <v>6</v>
+      </c>
+      <c r="G26" s="1">
+        <v>-0.1076</v>
+      </c>
+      <c r="H26" s="1">
+        <v>0.33019999999999999</v>
+      </c>
+      <c r="I26" s="1">
+        <v>-0.3357</v>
+      </c>
+      <c r="J26" s="3">
+        <v>3.3500000000000002E-2</v>
+      </c>
+      <c r="K26" s="1">
+        <v>24795.597300000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="1">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F27" s="1">
+        <v>3</v>
+      </c>
+      <c r="G27" s="1">
+        <v>-0.11799999999999999</v>
+      </c>
+      <c r="H27" s="1">
+        <v>0.4662</v>
+      </c>
+      <c r="I27" s="1">
+        <v>-0.1988</v>
+      </c>
+      <c r="J27" s="3">
+        <v>3.8899999999999997E-2</v>
+      </c>
+      <c r="K27" s="1">
+        <v>25067.428199999998</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="1">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F28" s="1">
+        <v>1</v>
+      </c>
+      <c r="G28" s="1">
+        <v>-5.6300000000000003E-2</v>
+      </c>
+      <c r="H28" s="1">
+        <v>0.88739999999999997</v>
+      </c>
+      <c r="I28" s="1">
+        <v>-3.73E-2</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0.26569999999999999</v>
+      </c>
+      <c r="K28" s="1">
+        <v>25064.140200000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A6:I6"/>
+    <mergeCell ref="A11:K11"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/graficos_tabelas/preliminares/Tabela_resumo_thetas.xlsx
+++ b/graficos_tabelas/preliminares/Tabela_resumo_thetas.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1073" documentId="11_F25DC773A252ABDACC1048C0F11B46C65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B58D5D75-4918-415F-9C4C-B32340697E2D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IBOV" sheetId="1" r:id="rId1"/>

--- a/graficos_tabelas/preliminares/Tabela_resumo_thetas.xlsx
+++ b/graficos_tabelas/preliminares/Tabela_resumo_thetas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6e8fc6e241c731ae/UFABC/Dissertação/volatilidade-IBOV-GPR/Impacto-geopolitico-ibovespa/graficos_tabelas/preliminares/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1073" documentId="11_F25DC773A252ABDACC1048C0F11B46C65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B58D5D75-4918-415F-9C4C-B32340697E2D}"/>
+  <xr:revisionPtr revIDLastSave="1154" documentId="11_F25DC773A252ABDACC1048C0F11B46C65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71CCA169-A15C-4795-A404-4A4E6A011FE5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IBOV" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="515">
   <si>
     <t>Garch-Midas nos retornos do Ibovespa</t>
   </si>
@@ -1007,9 +1007,6 @@
     <t>VARIANCIA DO CAMBIO X IBOV (SIMÉTRICO)</t>
   </si>
   <si>
-    <t>Assimetrico não muda tanto os resultados</t>
-  </si>
-  <si>
     <t>0.041</t>
   </si>
   <si>
@@ -1479,6 +1476,105 @@
   </si>
   <si>
     <t>MODELO 2 - GPR GLOBAL E VAR CAMBIO ASSIMÉTRICO - SETOR: ENERGIA</t>
+  </si>
+  <si>
+    <t>VARIANCIA DO CAMBIO X IBOV (ASIMÉTRICO)</t>
+  </si>
+  <si>
+    <t>-0.2322</t>
+  </si>
+  <si>
+    <t>0.233</t>
+  </si>
+  <si>
+    <t>-22.66</t>
+  </si>
+  <si>
+    <t>-21.78</t>
+  </si>
+  <si>
+    <t>-20.52</t>
+  </si>
+  <si>
+    <t>-0.2621</t>
+  </si>
+  <si>
+    <t>-0.3736</t>
+  </si>
+  <si>
+    <t>-0.1713</t>
+  </si>
+  <si>
+    <t>-0.7478</t>
+  </si>
+  <si>
+    <t>-0.4210</t>
+  </si>
+  <si>
+    <t>0.758</t>
+  </si>
+  <si>
+    <t>-0.3416</t>
+  </si>
+  <si>
+    <t>0.028</t>
+  </si>
+  <si>
+    <t>-0.1558</t>
+  </si>
+  <si>
+    <t>0.067</t>
+  </si>
+  <si>
+    <t>-0.0505</t>
+  </si>
+  <si>
+    <t>0.073</t>
+  </si>
+  <si>
+    <t>0.420</t>
+  </si>
+  <si>
+    <t>0.911</t>
+  </si>
+  <si>
+    <t>0.591</t>
+  </si>
+  <si>
+    <t>0.236</t>
+  </si>
+  <si>
+    <t>0.385</t>
+  </si>
+  <si>
+    <t>0.512</t>
+  </si>
+  <si>
+    <t>0.846</t>
+  </si>
+  <si>
+    <t>0.525</t>
+  </si>
+  <si>
+    <t>IC-BR X IBOV (ASSIMETRICO)</t>
+  </si>
+  <si>
+    <t>-0.1049</t>
+  </si>
+  <si>
+    <t>0.036</t>
+  </si>
+  <si>
+    <t>-0.0333</t>
+  </si>
+  <si>
+    <t>0.150</t>
+  </si>
+  <si>
+    <t>-0.0181</t>
+  </si>
+  <si>
+    <t>0.239</t>
   </si>
 </sst>
 </file>
@@ -1572,7 +1668,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1594,6 +1690,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1878,7 +1976,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L63"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.140625" customWidth="1"/>
@@ -2333,9 +2431,6 @@
       <c r="G27" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="H27" t="s">
-        <v>325</v>
-      </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
@@ -2345,7 +2440,7 @@
         <v>323</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>322</v>
@@ -2354,7 +2449,7 @@
         <v>167</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>95</v>
@@ -2365,27 +2460,27 @@
         <v>7</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>167</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>196</v>
       </c>
       <c r="F29" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>96</v>
+        <v>482</v>
       </c>
       <c r="B31" s="8"/>
       <c r="C31" s="8"/>
@@ -2393,954 +2488,1134 @@
       <c r="E31" s="8"/>
       <c r="F31" s="8"/>
       <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
-      <c r="J31" s="8"/>
-      <c r="K31" s="7"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B38" s="8"/>
+      <c r="C38" s="8"/>
+      <c r="D38" s="8"/>
+      <c r="E38" s="8"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="8"/>
+      <c r="I38" s="8"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="7"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B39" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D39" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E39" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F39" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G39" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="H39" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="I39" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="J32" s="1" t="s">
+      <c r="J39" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="L32" t="s">
+      <c r="L39" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="1">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="1">
         <v>12</v>
       </c>
-      <c r="D33" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" s="1">
+      <c r="D40" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F40" s="1">
         <v>12</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G40" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="H40" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="I33" s="1" t="s">
+      <c r="I40" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="J33" s="3" t="s">
+      <c r="J40" s="3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="1">
-        <v>6</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" s="1">
-        <v>6</v>
-      </c>
-      <c r="G34" s="1" t="s">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="1">
+        <v>6</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F41" s="1">
+        <v>6</v>
+      </c>
+      <c r="G41" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="H34" s="3" t="s">
+      <c r="H41" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="I34" s="1" t="s">
+      <c r="I41" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="J34" s="3" t="s">
+      <c r="J41" s="3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C35" s="1">
-        <v>3</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35" s="1">
-        <v>3</v>
-      </c>
-      <c r="G35" s="1" t="s">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="1">
+        <v>3</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F42" s="1">
+        <v>3</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="H42" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="I42" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="J35" s="3" t="s">
+      <c r="J42" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C36" s="1">
-        <v>3</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" s="1">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="1">
+        <v>3</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F43" s="1">
         <v>1</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G43" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="H43" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="I43" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="J36" s="3" t="s">
+      <c r="J43" s="3" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="1">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="1">
         <v>12</v>
       </c>
-      <c r="D37" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" s="1">
+      <c r="D44" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F44" s="1">
         <v>12</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G44" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="H44" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="I37" s="1" t="s">
+      <c r="I44" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="J37" s="3" t="s">
+      <c r="J44" s="3" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="1">
-        <v>6</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" s="1">
-        <v>6</v>
-      </c>
-      <c r="G38" s="1" t="s">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="1">
+        <v>6</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F45" s="1">
+        <v>6</v>
+      </c>
+      <c r="G45" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="H45" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="I45" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="J38" s="3" t="s">
+      <c r="J45" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="1">
-        <v>3</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" s="1">
-        <v>3</v>
-      </c>
-      <c r="G39" s="1" t="s">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="1">
+        <v>3</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F46" s="1">
+        <v>3</v>
+      </c>
+      <c r="G46" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="H46" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="I39" s="1" t="s">
+      <c r="I46" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="J39" s="5" t="s">
+      <c r="J46" s="5" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="1">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" s="1">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="1">
+        <v>3</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F47" s="1">
         <v>1</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G47" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H47" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="I40" s="1" t="s">
+      <c r="I47" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="J40" s="1" t="s">
+      <c r="J47" s="1" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="1">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="1">
         <v>12</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F41" s="1">
+      <c r="D48" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F48" s="1">
         <v>12</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G48" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H48" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="I48" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="J41" s="3" t="s">
+      <c r="J48" s="3" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="1">
-        <v>6</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F42" s="1">
-        <v>6</v>
-      </c>
-      <c r="G42" s="1" t="s">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="1">
+        <v>6</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F49" s="1">
+        <v>6</v>
+      </c>
+      <c r="G49" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="H49" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="I42" s="1" t="s">
+      <c r="I49" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="J42" s="3" t="s">
+      <c r="J49" s="3" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="1">
-        <v>3</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F43" s="1">
-        <v>3</v>
-      </c>
-      <c r="G43" s="1" t="s">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="1">
+        <v>3</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F50" s="1">
+        <v>3</v>
+      </c>
+      <c r="G50" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="H50" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="I43" s="1" t="s">
+      <c r="I50" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="J43" s="3" t="s">
+      <c r="J50" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="1">
-        <v>3</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F44" s="1">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="1">
+        <v>3</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F51" s="1">
         <v>1</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="G51" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="H51" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="I44" s="1" t="s">
+      <c r="I51" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="J44" s="3" t="s">
+      <c r="J51" s="3" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="1">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="1">
         <v>12</v>
       </c>
-      <c r="D45" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" s="1">
+      <c r="D52" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F52" s="1">
         <v>12</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="G52" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="H45" s="1" t="s">
+      <c r="H52" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="I45" s="1" t="s">
+      <c r="I52" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="J45" s="3" t="s">
+      <c r="J52" s="3" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="1">
-        <v>6</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F46" s="1">
-        <v>6</v>
-      </c>
-      <c r="G46" s="1" t="s">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="1">
+        <v>6</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F53" s="1">
+        <v>6</v>
+      </c>
+      <c r="G53" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="H53" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="I46" s="1" t="s">
+      <c r="I53" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="J46" s="3" t="s">
+      <c r="J53" s="3" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="1">
-        <v>3</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F47" s="1">
-        <v>3</v>
-      </c>
-      <c r="G47" s="1" t="s">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="1">
+        <v>3</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F54" s="1">
+        <v>3</v>
+      </c>
+      <c r="G54" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="H54" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="I47" s="1" t="s">
+      <c r="I54" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="J47" s="1" t="s">
+      <c r="J54" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="1">
-        <v>3</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" s="1">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="1">
+        <v>3</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F55" s="1">
         <v>1</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="G55" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="H48" s="5" t="s">
+      <c r="H55" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="I48" s="1" t="s">
+      <c r="I55" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="J48" s="1" t="s">
+      <c r="J55" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" s="8" t="s">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="8" t="s">
+        <v>437</v>
+      </c>
+      <c r="B57" s="8"/>
+      <c r="C57" s="8"/>
+      <c r="D57" s="8"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="8"/>
+      <c r="G57" s="8"/>
+    </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59" s="4" t="s">
         <v>438</v>
       </c>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="8"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
+      <c r="C59" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="11"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="11"/>
+      <c r="D60" s="11"/>
+      <c r="E60" s="11"/>
+      <c r="F60" s="11"/>
+      <c r="G60" s="11"/>
+    </row>
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="B61" s="8"/>
+      <c r="C61" s="8"/>
+      <c r="D61" s="8"/>
+      <c r="E61" s="8"/>
+      <c r="F61" s="8"/>
+      <c r="G61" s="8"/>
+    </row>
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B62" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C62" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D51" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E51" s="1" t="s">
+      <c r="D62" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="F62" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="G62" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B52" s="4" t="s">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="1"/>
+      <c r="B64" s="4"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="B65" s="8"/>
+      <c r="C65" s="8"/>
+      <c r="D65" s="8"/>
+      <c r="E65" s="8"/>
+      <c r="F65" s="8"/>
+      <c r="G65" s="8"/>
+      <c r="H65" s="8"/>
+      <c r="I65" s="8"/>
+      <c r="J65" s="8"/>
+      <c r="K65" s="8"/>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="1">
+        <v>12</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F67" s="1">
+        <v>12</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>447</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="1">
+        <v>6</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F68" s="1">
+        <v>6</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="I68" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J68" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="1">
+        <v>3</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F69" s="1">
+        <v>3</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="I69" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="1">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F70" s="1">
+        <v>1</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="1">
+        <v>12</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F71" s="1">
+        <v>12</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="1">
+        <v>6</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F72" s="1">
+        <v>6</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="1">
+        <v>3</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F73" s="1">
+        <v>3</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="1">
+        <v>3</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F74" s="1">
+        <v>1</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="H74" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" s="8" t="s">
-        <v>445</v>
-      </c>
-      <c r="B54" s="8"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
-      <c r="G54" s="8"/>
-      <c r="H54" s="8"/>
-      <c r="I54" s="8"/>
-      <c r="J54" s="8"/>
-      <c r="K54" s="8"/>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H55" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="I55" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="J55" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C56" s="1">
-        <v>12</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F56" s="1">
-        <v>12</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>447</v>
-      </c>
-      <c r="H56" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="I56" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57" s="1">
-        <v>6</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F57" s="1">
-        <v>6</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="I57" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J57" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C58" s="1">
-        <v>3</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F58" s="1">
-        <v>3</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="J58" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C59" s="1">
-        <v>3</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F59" s="1">
-        <v>1</v>
-      </c>
-      <c r="G59" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="J59" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" s="1">
-        <v>12</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F60" s="1">
-        <v>12</v>
-      </c>
-      <c r="G60" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="H60" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="I60" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="J60" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" s="1">
-        <v>6</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F61" s="1">
-        <v>6</v>
-      </c>
-      <c r="G61" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="H61" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="I61" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="J61" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A62" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" s="1">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F62" s="1">
-        <v>3</v>
-      </c>
-      <c r="G62" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="H62" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="I62" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="J62" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="K62" s="1" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A63" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C63" s="1">
-        <v>3</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>446</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F63" s="1">
-        <v>1</v>
-      </c>
-      <c r="G63" s="1" t="s">
+      <c r="I74" s="1" t="s">
         <v>479</v>
       </c>
-      <c r="H63" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="I63" s="1" t="s">
+      <c r="J74" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="K74" s="1" t="s">
         <v>480</v>
       </c>
-      <c r="J63" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>481</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A50:G50"/>
-    <mergeCell ref="A54:K54"/>
+  <mergeCells count="9">
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A65:K65"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A38:J38"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A61:G61"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3875,14 +4150,30 @@
       <c r="A9" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
+      <c r="B9" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>499</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
@@ -4551,7 +4842,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -5275,19 +5566,19 @@
         <v>42</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>500</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>41</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>115</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>40</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>16</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -5298,24 +5589,24 @@
         <v>61</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>501</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>62</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
+        <v>371</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>63</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>16</v>
+        <v>502</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -5360,28 +5651,28 @@
         <v>148</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>341</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -5389,33 +5680,33 @@
         <v>149</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>344</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>346</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>347</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="I9" s="1" t="s">
         <v>349</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -5460,7 +5751,7 @@
         <v>80</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -5483,19 +5774,19 @@
         <v>12</v>
       </c>
       <c r="G14" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>353</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>354</v>
       </c>
-      <c r="J14" s="1" t="s">
+      <c r="K14" s="1" t="s">
         <v>355</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -5518,19 +5809,19 @@
         <v>6</v>
       </c>
       <c r="G15" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="J15" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="J15" s="1" t="s">
+      <c r="K15" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -5553,19 +5844,19 @@
         <v>3</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H16" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="J16" s="5" t="s">
         <v>363</v>
       </c>
-      <c r="I16" s="1" t="s">
-        <v>362</v>
-      </c>
-      <c r="J16" s="5" t="s">
+      <c r="K16" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -5588,19 +5879,19 @@
         <v>1</v>
       </c>
       <c r="G17" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>368</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="K17" s="1" t="s">
         <v>369</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -5623,19 +5914,19 @@
         <v>12</v>
       </c>
       <c r="G18" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="I18" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>373</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>194</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -5658,19 +5949,19 @@
         <v>6</v>
       </c>
       <c r="G19" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="I19" s="1" t="s">
         <v>376</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>377</v>
       </c>
       <c r="J19" s="1" t="s">
         <v>140</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -5696,16 +5987,16 @@
         <v>240</v>
       </c>
       <c r="H20" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="I20" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="J20" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="J20" s="1" t="s">
+      <c r="K20" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -5728,19 +6019,19 @@
         <v>1</v>
       </c>
       <c r="G21" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="I21" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="J21" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="K21" s="1" t="s">
         <v>386</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -5763,19 +6054,19 @@
         <v>12</v>
       </c>
       <c r="G22" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>389</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="J22" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="J22" s="1" t="s">
+      <c r="K22" s="1" t="s">
         <v>391</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -5798,19 +6089,19 @@
         <v>6</v>
       </c>
       <c r="G23" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="J23" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="J23" s="1" t="s">
+      <c r="K23" s="1" t="s">
         <v>396</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -5833,19 +6124,19 @@
         <v>3</v>
       </c>
       <c r="G24" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>398</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="I24" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>400</v>
       </c>
       <c r="J24" s="1" t="s">
         <v>105</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -5868,19 +6159,19 @@
         <v>1</v>
       </c>
       <c r="G25" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="I25" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="J25" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="J25" s="1" t="s">
+      <c r="K25" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -5903,19 +6194,19 @@
         <v>12</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>407</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="I26" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="J26" s="5" t="s">
         <v>409</v>
       </c>
-      <c r="J26" s="5" t="s">
+      <c r="K26" s="1" t="s">
         <v>410</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -5938,19 +6229,19 @@
         <v>6</v>
       </c>
       <c r="G27" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="H27" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="I27" s="1" t="s">
         <v>413</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>414</v>
       </c>
       <c r="J27" s="1" t="s">
         <v>145</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -5973,19 +6264,19 @@
         <v>3</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>308</v>
       </c>
       <c r="I28" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="J28" s="1" t="s">
         <v>417</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="K28" s="1" t="s">
         <v>418</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -6008,16 +6299,16 @@
         <v>1</v>
       </c>
       <c r="G29" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="I29" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="J29" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>423</v>
       </c>
       <c r="K29" s="1">
         <v>25110</v>
@@ -6090,19 +6381,19 @@
         <v>52</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>501</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>16</v>
+        <v>503</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>54</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>16</v>
+        <v>504</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -6113,24 +6404,24 @@
         <v>69</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>505</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>70</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
+        <v>506</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>71</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>16</v>
+        <v>507</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -6175,28 +6466,28 @@
         <v>148</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>430</v>
-      </c>
       <c r="I8" s="1" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -6204,33 +6495,33 @@
         <v>318</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>177</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="G9" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="1" t="s">
         <v>435</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="I9" s="1" t="s">
         <v>436</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -6275,7 +6566,7 @@
         <v>80</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">

--- a/graficos_tabelas/preliminares/Tabela_resumo_thetas.xlsx
+++ b/graficos_tabelas/preliminares/Tabela_resumo_thetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6e8fc6e241c731ae/UFABC/Dissertação/volatilidade-IBOV-GPR/Impacto-geopolitico-ibovespa/graficos_tabelas/preliminares/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1154" documentId="11_F25DC773A252ABDACC1048C0F11B46C65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71CCA169-A15C-4795-A404-4A4E6A011FE5}"/>
+  <xr:revisionPtr revIDLastSave="1157" documentId="11_F25DC773A252ABDACC1048C0F11B46C65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBC35226-9B21-498A-9F4F-386681493409}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="517">
   <si>
     <t>Garch-Midas nos retornos do Ibovespa</t>
   </si>
@@ -1575,6 +1575,12 @@
   </si>
   <si>
     <t>0.239</t>
+  </si>
+  <si>
+    <t>-0.3043</t>
+  </si>
+  <si>
+    <t>0.053</t>
   </si>
 </sst>
 </file>
@@ -1668,7 +1674,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1681,6 +1687,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1690,8 +1697,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2008,15 +2013,15 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -2126,15 +2131,15 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -2229,15 +2234,15 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
@@ -2376,15 +2381,15 @@
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
+      <c r="A25" s="9" t="s">
         <v>324</v>
       </c>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
@@ -2437,10 +2442,10 @@
         <v>6</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>325</v>
+        <v>515</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>516</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>322</v>
@@ -2479,15 +2484,15 @@
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="9" t="s">
         <v>482</v>
       </c>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
-      <c r="D31" s="8"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
@@ -2582,18 +2587,18 @@
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
-      <c r="I38" s="8"/>
-      <c r="J38" s="8"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
       <c r="K38" s="7"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
@@ -3144,15 +3149,15 @@
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A57" s="8" t="s">
+      <c r="A57" s="9" t="s">
         <v>437</v>
       </c>
-      <c r="B57" s="8"/>
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8"/>
-      <c r="G57" s="8"/>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="9"/>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
@@ -3201,24 +3206,18 @@
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A60" s="11"/>
-      <c r="B60" s="12"/>
-      <c r="C60" s="11"/>
-      <c r="D60" s="11"/>
-      <c r="E60" s="11"/>
-      <c r="F60" s="11"/>
-      <c r="G60" s="11"/>
+      <c r="B60" s="8"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="9" t="s">
         <v>508</v>
       </c>
-      <c r="B61" s="8"/>
-      <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8"/>
-      <c r="G61" s="8"/>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
+      <c r="F61" s="9"/>
+      <c r="G61" s="9"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
@@ -3276,19 +3275,19 @@
       <c r="G64" s="1"/>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="9" t="s">
         <v>444</v>
       </c>
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="8"/>
-      <c r="G65" s="8"/>
-      <c r="H65" s="8"/>
-      <c r="I65" s="8"/>
-      <c r="J65" s="8"/>
-      <c r="K65" s="8"/>
+      <c r="B65" s="9"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="9"/>
+      <c r="E65" s="9"/>
+      <c r="F65" s="9"/>
+      <c r="G65" s="9"/>
+      <c r="H65" s="9"/>
+      <c r="I65" s="9"/>
+      <c r="J65" s="9"/>
+      <c r="K65" s="9"/>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
@@ -3648,15 +3647,15 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -3728,15 +3727,15 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
@@ -3808,15 +3807,15 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -3888,15 +3887,15 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
@@ -3996,15 +3995,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4076,17 +4075,17 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -4176,18 +4175,18 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -4761,15 +4760,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -4841,17 +4840,17 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -4941,18 +4940,18 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -5525,15 +5524,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -5605,17 +5604,17 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -5705,19 +5704,19 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="9" t="s">
         <v>331</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -6340,15 +6339,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
@@ -6420,17 +6419,17 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>423</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
-      <c r="I6" s="8"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -6520,19 +6519,19 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="9" t="s">
         <v>481</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="9"/>
+      <c r="K11" s="9"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">

--- a/graficos_tabelas/preliminares/Tabela_resumo_thetas.xlsx
+++ b/graficos_tabelas/preliminares/Tabela_resumo_thetas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6e8fc6e241c731ae/UFABC/Dissertação/volatilidade-IBOV-GPR/Impacto-geopolitico-ibovespa/graficos_tabelas/preliminares/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1157" documentId="11_F25DC773A252ABDACC1048C0F11B46C65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EBC35226-9B21-498A-9F4F-386681493409}"/>
+  <xr:revisionPtr revIDLastSave="1163" documentId="11_F25DC773A252ABDACC1048C0F11B46C65ADE58EB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31F92FE9-3007-424B-B2DF-CF2A3E88C64C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IBOV" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="520">
   <si>
     <t>Garch-Midas nos retornos do Ibovespa</t>
   </si>
@@ -1581,6 +1581,15 @@
   </si>
   <si>
     <t>0.053</t>
+  </si>
+  <si>
+    <t>0.6480</t>
+  </si>
+  <si>
+    <t>-0.1373</t>
+  </si>
+  <si>
+    <t>0.541</t>
   </si>
 </sst>
 </file>
@@ -4033,10 +4042,10 @@
         <v>39</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>44</v>
+        <v>517</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>119</v>
+        <v>246</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>45</v>
@@ -6377,10 +6386,10 @@
         <v>39</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>52</v>
+        <v>518</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>501</v>
+        <v>519</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>53</v>
